--- a/outputs/paul_asset_allocation_model.xlsx
+++ b/outputs/paul_asset_allocation_model.xlsx
@@ -9,13 +9,11 @@
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Asset Inputs" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Average Detail" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="MVO Detail" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Monte Carlo" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Scenario Detail" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Constraints" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Checks" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Sources and Setup" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="MVO Detail" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Scenario Detail" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Constraints" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Checks" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Sources and Setup" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,10 +22,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="0.00x"/>
-    <numFmt numFmtId="166" formatCode="0.000%"/>
+    <numFmt numFmtId="165" formatCode="0.000%"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -94,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -120,13 +117,10 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -709,7 +703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K33"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -784,7 +778,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Main allocation is the 50/50 average of target-volatility optimization and Monte Carlo target-volatility search.</t>
+          <t>Main allocation is the target-volatility MVO result. Monte Carlo simulation is currently removed from all calculations.</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -867,7 +861,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Main Recommended Allocation: Average of MVO and Monte Carlo</t>
+          <t>Main Recommended Allocation: MVO</t>
         </is>
       </c>
       <c r="B9" s="2" t="n"/>
@@ -945,31 +939,31 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>0.055137</v>
+        <v>0.05756</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>0.081986</v>
+        <v>0.083325</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>0.294407</v>
+        <v>0.318757</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.356325</v>
+        <v>0.302111</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.627717</v>
+        <v>0.687889</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.005959</v>
+        <v>0</v>
       </c>
       <c r="H11" s="5" t="n">
         <v>0.01</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0.07200000000000001</v>
+        <v>0.07332472972620824</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>0.08200000000000002</v>
+        <v>0.08332472972620825</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
@@ -984,31 +978,31 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>0.060704</v>
+        <v>0.06447</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>0.109974</v>
+        <v>0.115447</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>0.2701</v>
+        <v>0.289915</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0.583986</v>
+        <v>0.55</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.405614</v>
+        <v>0.44</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.000401</v>
+        <v>0</v>
       </c>
       <c r="H12" s="5" t="n">
         <v>0.01</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.1</v>
+        <v>0.1054471964394289</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0.11</v>
+        <v>0.1154471964394289</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
@@ -1023,31 +1017,31 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>0.06456199999999999</v>
+        <v>0.066319</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0.130897</v>
+        <v>0.129065</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>0.2564</v>
+        <v>0.27365</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0.739992</v>
+        <v>0.65</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.250005</v>
+        <v>0.34</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>4e-06</v>
+        <v>0</v>
       </c>
       <c r="H13" s="5" t="n">
         <v>0.01</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>0.127</v>
+        <v>0.1230651077209465</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>0.133</v>
+        <v>0.1290651077209465</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
@@ -1062,35 +1056,35 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>0.06777900000000001</v>
+        <v>0.06858599999999999</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>0.14942</v>
+        <v>0.147783</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>0.246145</v>
+        <v>0.254334</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0.849207</v>
+        <v>0.817936</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.100114</v>
+        <v>0.172064</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.04068</v>
+        <v>0</v>
       </c>
       <c r="H14" s="5" t="n">
         <v>0.01</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>0.153</v>
+        <v>0.1377832186992815</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>0.163</v>
+        <v>0.1477832186992815</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Below target</t>
+          <t>In target</t>
         </is>
       </c>
     </row>
@@ -1101,35 +1095,35 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>0.070752</v>
+        <v>0.07063999999999999</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>0.165733</v>
+        <v>0.167147</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>0.239853</v>
+        <v>0.237157</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.989965</v>
+        <v>0.99</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1.9e-05</v>
+        <v>0</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>1.6e-05</v>
+        <v>0</v>
       </c>
       <c r="H15" s="5" t="n">
         <v>0.01</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>0.18</v>
+        <v>0.1576876655884257</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>0.19</v>
+        <v>0.1676876655884257</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>Below target</t>
+          <t>In target</t>
         </is>
       </c>
     </row>
@@ -1240,19 +1234,19 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>0.055149</v>
+        <v>0.05756</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>0.082</v>
+        <v>0.083325</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>0.294498</v>
+        <v>0.318757</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0.359831</v>
+        <v>0.302111</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0.630169</v>
+        <v>0.687889</v>
       </c>
       <c r="G20" s="5" t="n">
         <v>0</v>
@@ -1261,10 +1255,10 @@
         <v>0.01</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>0.07200000000000001</v>
+        <v>0.07332472972620824</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>0.08200000000000002</v>
+        <v>0.08332472972620825</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
@@ -1279,19 +1273,19 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>0.06071</v>
+        <v>0.06447</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>0.11</v>
+        <v>0.115447</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>0.270088</v>
+        <v>0.289915</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0.584416</v>
+        <v>0.55</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.405584</v>
+        <v>0.44</v>
       </c>
       <c r="G21" s="5" t="n">
         <v>0</v>
@@ -1300,10 +1294,10 @@
         <v>0.01</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>0.1</v>
+        <v>0.1054471964394289</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>0.11</v>
+        <v>0.1154471964394289</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
@@ -1318,19 +1312,19 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>0.06456199999999999</v>
+        <v>0.066319</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>0.130897</v>
+        <v>0.129065</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>0.2564</v>
+        <v>0.27365</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0.74</v>
+        <v>0.65</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.25</v>
+        <v>0.34</v>
       </c>
       <c r="G22" s="5" t="n">
         <v>0</v>
@@ -1339,10 +1333,10 @@
         <v>0.01</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>0.127</v>
+        <v>0.1230651077209465</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>0.133</v>
+        <v>0.1290651077209465</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
@@ -1357,35 +1351,35 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>0.06779</v>
+        <v>0.06858599999999999</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>0.149472</v>
+        <v>0.147783</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>0.246133</v>
+        <v>0.254334</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0.85</v>
+        <v>0.817936</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0.1</v>
+        <v>0.172064</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="H23" s="5" t="n">
         <v>0.01</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>0.153</v>
+        <v>0.1377832186992815</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>0.163</v>
+        <v>0.1477832186992815</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>Below target</t>
+          <t>In target</t>
         </is>
       </c>
     </row>
@@ -1396,13 +1390,13 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>0.070752</v>
+        <v>0.07063999999999999</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>0.165737</v>
+        <v>0.167147</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>0.239852</v>
+        <v>0.237157</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>0.99</v>
@@ -1417,317 +1411,21 @@
         <v>0.01</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>0.18</v>
+        <v>0.1576876655884257</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>0.19</v>
+        <v>0.1676876655884257</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>Below target</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n"/>
-      <c r="B25" s="2" t="n"/>
-      <c r="C25" s="2" t="n"/>
-      <c r="D25" s="2" t="n"/>
-      <c r="E25" s="2" t="n"/>
-      <c r="F25" s="2" t="n"/>
-      <c r="G25" s="2" t="n"/>
-      <c r="H25" s="2" t="n"/>
-      <c r="I25" s="2" t="n"/>
-      <c r="J25" s="2" t="n"/>
-      <c r="K25" s="2" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n"/>
-      <c r="B26" s="2" t="n"/>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n"/>
-      <c r="E26" s="2" t="n"/>
-      <c r="F26" s="2" t="n"/>
-      <c r="G26" s="2" t="n"/>
-      <c r="H26" s="2" t="n"/>
-      <c r="I26" s="2" t="n"/>
-      <c r="J26" s="2" t="n"/>
-      <c r="K26" s="2" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>Monte Carlo Target Volatility Overall Allocation</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n"/>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="n"/>
-      <c r="E27" s="2" t="n"/>
-      <c r="F27" s="2" t="n"/>
-      <c r="G27" s="2" t="n"/>
-      <c r="H27" s="2" t="n"/>
-      <c r="I27" s="2" t="n"/>
-      <c r="J27" s="2" t="n"/>
-      <c r="K27" s="2" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>Portfolio</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>Expected Return</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>Volatility</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>Sharpe vs Cash</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>Fixed Income</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>Alternatives</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>Cash</t>
-        </is>
-      </c>
-      <c r="I28" s="4" t="inlineStr">
-        <is>
-          <t>Target Vol Min</t>
-        </is>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>Target Vol Max</t>
-        </is>
-      </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>Target Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>Conservative</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="n">
-        <v>0.055125</v>
-      </c>
-      <c r="C29" s="5" t="n">
-        <v>0.08197500000000001</v>
-      </c>
-      <c r="D29" s="6" t="n">
-        <v>0.294303</v>
-      </c>
-      <c r="E29" s="5" t="n">
-        <v>0.352819</v>
-      </c>
-      <c r="F29" s="5" t="n">
-        <v>0.625264</v>
-      </c>
-      <c r="G29" s="5" t="n">
-        <v>0.011918</v>
-      </c>
-      <c r="H29" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I29" s="5" t="n">
-        <v>0.07200000000000001</v>
-      </c>
-      <c r="J29" s="5" t="n">
-        <v>0.08200000000000002</v>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
           <t>In target</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>Balanced</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="n">
-        <v>0.060699</v>
-      </c>
-      <c r="C30" s="5" t="n">
-        <v>0.109949</v>
-      </c>
-      <c r="D30" s="6" t="n">
-        <v>0.270112</v>
-      </c>
-      <c r="E30" s="5" t="n">
-        <v>0.583555</v>
-      </c>
-      <c r="F30" s="5" t="n">
-        <v>0.405643</v>
-      </c>
-      <c r="G30" s="5" t="n">
-        <v>0.000801</v>
-      </c>
-      <c r="H30" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I30" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J30" s="5" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>In target</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="n">
-        <v>0.06456199999999999</v>
-      </c>
-      <c r="C31" s="5" t="n">
-        <v>0.130896</v>
-      </c>
-      <c r="D31" s="6" t="n">
-        <v>0.256401</v>
-      </c>
-      <c r="E31" s="5" t="n">
-        <v>0.739984</v>
-      </c>
-      <c r="F31" s="5" t="n">
-        <v>0.250009</v>
-      </c>
-      <c r="G31" s="5" t="n">
-        <v>7e-06</v>
-      </c>
-      <c r="H31" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I31" s="5" t="n">
-        <v>0.127</v>
-      </c>
-      <c r="J31" s="5" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>In target</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Growth</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="n">
-        <v>0.06776799999999999</v>
-      </c>
-      <c r="C32" s="5" t="n">
-        <v>0.149368</v>
-      </c>
-      <c r="D32" s="6" t="n">
-        <v>0.246157</v>
-      </c>
-      <c r="E32" s="5" t="n">
-        <v>0.848413</v>
-      </c>
-      <c r="F32" s="5" t="n">
-        <v>0.100227</v>
-      </c>
-      <c r="G32" s="5" t="n">
-        <v>0.041359</v>
-      </c>
-      <c r="H32" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I32" s="5" t="n">
-        <v>0.153</v>
-      </c>
-      <c r="J32" s="5" t="n">
-        <v>0.163</v>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>Below target</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>Aggressive Growth</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="n">
-        <v>0.07075099999999999</v>
-      </c>
-      <c r="C33" s="5" t="n">
-        <v>0.16573</v>
-      </c>
-      <c r="D33" s="6" t="n">
-        <v>0.239854</v>
-      </c>
-      <c r="E33" s="5" t="n">
-        <v>0.9899289999999999</v>
-      </c>
-      <c r="F33" s="5" t="n">
-        <v>3.8e-05</v>
-      </c>
-      <c r="G33" s="5" t="n">
-        <v>3.3e-05</v>
-      </c>
-      <c r="H33" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I33" s="5" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="J33" s="5" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>Below target</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="2">
     <mergeCell ref="A18:K18"/>
     <mergeCell ref="A9:K9"/>
-    <mergeCell ref="A27:K27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1991,7 +1689,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -2025,7 +1723,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -2343,19 +2041,19 @@
         </is>
       </c>
       <c r="C2" s="5" t="n">
-        <v>0.178162</v>
+        <v>0.2</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>0.291993</v>
+        <v>0.239219</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0.369996</v>
+        <v>0.2</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>0.424603</v>
+        <v>0.317936</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.494982</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="3">
@@ -2370,19 +2068,19 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>0.054819</v>
+        <v>0</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>0.08984399999999999</v>
+        <v>0.02115</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0.113845</v>
+        <v>0.15</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.130647</v>
+        <v>0.2</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.152302</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="4">
@@ -2397,19 +2095,19 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>0.013705</v>
+        <v>0</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>0.022461</v>
+        <v>0</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0.028461</v>
+        <v>0</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.032662</v>
+        <v>0</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.038076</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="5">
@@ -2424,19 +2122,19 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>0.082229</v>
+        <v>0.102111</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0.134766</v>
+        <v>0.2</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.170767</v>
+        <v>0.2</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.195971</v>
+        <v>0.2</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.228453</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="6">
@@ -2451,19 +2149,19 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>0.02741</v>
+        <v>0</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>0.044922</v>
+        <v>0.089631</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.056922</v>
+        <v>0.1</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.06532399999999999</v>
+        <v>0.1</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.076151</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="7">
@@ -2478,19 +2176,19 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0.002979</v>
+        <v>0</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>2e-06</v>
+        <v>0</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.02034</v>
+        <v>0</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>8e-06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -2505,19 +2203,19 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>0.002979</v>
+        <v>0</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>2e-06</v>
+        <v>0</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.02034</v>
+        <v>0</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>8e-06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -2532,19 +2230,19 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0.2108</v>
+        <v>0.002264</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>0.136214</v>
+        <v>0</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.083957</v>
+        <v>0</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.03362</v>
+        <v>0</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>6e-06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -2559,19 +2257,19 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>0.163956</v>
+        <v>0.145625</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>0.105944</v>
+        <v>0</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.0653</v>
+        <v>0</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.026149</v>
+        <v>0</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>5e-06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -2586,19 +2284,19 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>0.187378</v>
+        <v>0.4</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>0.121079</v>
+        <v>0.311147</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.074628</v>
+        <v>0.301335</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.029885</v>
+        <v>0.162064</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>6e-06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -2613,16 +2311,16 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>0.014053</v>
+        <v>0.03</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>0.009081000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0.005597</v>
+        <v>0.028665</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.002241</v>
+        <v>0</v>
       </c>
       <c r="G12" s="5" t="n">
         <v>0</v>
@@ -2640,19 +2338,19 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0.046845</v>
+        <v>0.1</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>0.03027</v>
+        <v>0.088853</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0.018657</v>
+        <v>0</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.007471</v>
+        <v>0</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>1e-06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -2667,16 +2365,16 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>0.004684</v>
+        <v>0.01</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>0.003027</v>
+        <v>0.01</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0.001866</v>
+        <v>0.01</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.0007470000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="G14" s="5" t="n">
         <v>0</v>
@@ -2720,23 +2418,23 @@
           <t>Check</t>
         </is>
       </c>
-      <c r="C16" s="5">
+      <c r="C16" s="8">
         <f>SUM(C2:C15)</f>
         <v/>
       </c>
-      <c r="D16" s="5">
+      <c r="D16" s="8">
         <f>SUM(D2:D15)</f>
         <v/>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="8">
         <f>SUM(E2:E15)</f>
         <v/>
       </c>
-      <c r="F16" s="5">
+      <c r="F16" s="8">
         <f>SUM(F2:F15)</f>
         <v/>
       </c>
-      <c r="G16" s="5">
+      <c r="G16" s="8">
         <f>SUM(G2:G15)</f>
         <v/>
       </c>
@@ -2747,1185 +2445,6 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Conservative</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Balanced</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Growth</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Aggressive Growth</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>U.S. Large Cap</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="n">
-        <v>0.179915</v>
-      </c>
-      <c r="D2" s="5" t="n">
-        <v>0.292208</v>
-      </c>
-      <c r="E2" s="5" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="F2" s="5" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="G2" s="5" t="n">
-        <v>0.495</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>U.S. Mid Cap</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="n">
-        <v>0.055359</v>
-      </c>
-      <c r="D3" s="5" t="n">
-        <v>0.08991</v>
-      </c>
-      <c r="E3" s="5" t="n">
-        <v>0.113846</v>
-      </c>
-      <c r="F3" s="5" t="n">
-        <v>0.130769</v>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>0.152308</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>U.S. Small Cap</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="n">
-        <v>0.01384</v>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>0.022478</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>0.028462</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>0.032692</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>0.038077</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>International Developed Equity</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>0.083038</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>0.134865</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>0.170769</v>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>0.196154</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>0.228462</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Emerging Markets Equity</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>0.027679</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>0.044955</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>0.056923</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>0.065385</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>0.076154</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>U.S. REITs</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Alternatives</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Commodities</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Alternatives</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Income U.S. - U.S. Treasury</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Fixed Income</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>0.211624</v>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>0.136204</v>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>0.083955</v>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>0.033582</v>
-      </c>
-      <c r="G9" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Income U.S. Government Related</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Fixed Income</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>0.164596</v>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>0.105936</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>0.065299</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>0.026119</v>
-      </c>
-      <c r="G10" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Income U.S. Corporate</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Fixed Income</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="n">
-        <v>0.18811</v>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>0.12107</v>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>0.074627</v>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>0.029851</v>
-      </c>
-      <c r="G11" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Income U.S. Securitized</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Fixed Income</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>0.014108</v>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>0.00908</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>0.005597</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>0.002239</v>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Fixed Income International</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Fixed Income</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="n">
-        <v>0.047028</v>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>0.030267</v>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>0.018657</v>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>0.007463</v>
-      </c>
-      <c r="G13" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Other Fixed Income</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Fixed Income</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="n">
-        <v>0.004703</v>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>0.003027</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>0.001866</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>0.000746</v>
-      </c>
-      <c r="G14" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Cash</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Cash</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="E15" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G15" s="5" t="n">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="C16" s="8">
-        <f>SUM(C2:C15)</f>
-        <v/>
-      </c>
-      <c r="D16" s="8">
-        <f>SUM(D2:D15)</f>
-        <v/>
-      </c>
-      <c r="E16" s="8">
-        <f>SUM(E2:E15)</f>
-        <v/>
-      </c>
-      <c r="F16" s="8">
-        <f>SUM(F2:F15)</f>
-        <v/>
-      </c>
-      <c r="G16" s="8">
-        <f>SUM(G2:G15)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Portfolio</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Expected Return</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Volatility</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Sharpe</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>$1 10Y Mean</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>$1 10Y P5</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>$1 10Y Median</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>$1 10Y P95</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Probability of Loss</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Conservative</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="n">
-        <v>0.055125</v>
-      </c>
-      <c r="C2" s="5" t="n">
-        <v>0.08197500000000001</v>
-      </c>
-      <c r="D2" s="5" t="n">
-        <v>0.294303</v>
-      </c>
-      <c r="E2" s="9" t="n">
-        <v>1.7197</v>
-      </c>
-      <c r="F2" s="9" t="n">
-        <v>1.1256</v>
-      </c>
-      <c r="G2" s="9" t="n">
-        <v>1.6756</v>
-      </c>
-      <c r="H2" s="9" t="n">
-        <v>2.4972</v>
-      </c>
-      <c r="I2" s="5" t="n">
-        <v>0.016667</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Balanced</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="n">
-        <v>0.060699</v>
-      </c>
-      <c r="C3" s="5" t="n">
-        <v>0.109949</v>
-      </c>
-      <c r="D3" s="5" t="n">
-        <v>0.270112</v>
-      </c>
-      <c r="E3" s="9" t="n">
-        <v>1.7819</v>
-      </c>
-      <c r="F3" s="9" t="n">
-        <v>0.9761</v>
-      </c>
-      <c r="G3" s="9" t="n">
-        <v>1.6902</v>
-      </c>
-      <c r="H3" s="9" t="n">
-        <v>2.814</v>
-      </c>
-      <c r="I3" s="5" t="n">
-        <v>0.064</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n">
-        <v>0.06456199999999999</v>
-      </c>
-      <c r="C4" s="5" t="n">
-        <v>0.130896</v>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>0.256401</v>
-      </c>
-      <c r="E4" s="9" t="n">
-        <v>1.8816</v>
-      </c>
-      <c r="F4" s="9" t="n">
-        <v>0.9109</v>
-      </c>
-      <c r="G4" s="9" t="n">
-        <v>1.7744</v>
-      </c>
-      <c r="H4" s="9" t="n">
-        <v>3.1695</v>
-      </c>
-      <c r="I4" s="5" t="n">
-        <v>0.077333</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Growth</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>0.06776799999999999</v>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>0.149368</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>0.246157</v>
-      </c>
-      <c r="E5" s="9" t="n">
-        <v>1.9543</v>
-      </c>
-      <c r="F5" s="9" t="n">
-        <v>0.8499</v>
-      </c>
-      <c r="G5" s="9" t="n">
-        <v>1.7977</v>
-      </c>
-      <c r="H5" s="9" t="n">
-        <v>3.6274</v>
-      </c>
-      <c r="I5" s="5" t="n">
-        <v>0.099333</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Aggressive Growth</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n">
-        <v>0.07075099999999999</v>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>0.16573</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>0.239854</v>
-      </c>
-      <c r="E6" s="9" t="n">
-        <v>1.9859</v>
-      </c>
-      <c r="F6" s="9" t="n">
-        <v>0.7137</v>
-      </c>
-      <c r="G6" s="9" t="n">
-        <v>1.7597</v>
-      </c>
-      <c r="H6" s="9" t="n">
-        <v>3.9742</v>
-      </c>
-      <c r="I6" s="5" t="n">
-        <v>0.138</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n"/>
-      <c r="B7" s="2" t="n"/>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
-      <c r="G7" s="2" t="n"/>
-      <c r="H7" s="2" t="n"/>
-      <c r="I7" s="2" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n"/>
-      <c r="B8" s="2" t="n"/>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="n"/>
-      <c r="G8" s="2" t="n"/>
-      <c r="H8" s="2" t="n"/>
-      <c r="I8" s="2" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>Monte Carlo Portfolio Weights</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n"/>
-      <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="n"/>
-      <c r="E9" s="2" t="n"/>
-      <c r="F9" s="2" t="n"/>
-      <c r="G9" s="2" t="n"/>
-      <c r="H9" s="2" t="n"/>
-      <c r="I9" s="2" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Conservative</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Balanced</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Growth</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Aggressive Growth</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="n"/>
-      <c r="I10" s="2" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>U.S. Large Cap</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="n">
-        <v>0.176409</v>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>0.291778</v>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>0.369992</v>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>0.424207</v>
-      </c>
-      <c r="G11" s="5" t="n">
-        <v>0.494965</v>
-      </c>
-      <c r="H11" s="2" t="n"/>
-      <c r="I11" s="2" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>U.S. Mid Cap</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>0.05428</v>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>0.089778</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>0.113844</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>0.130525</v>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>0.152297</v>
-      </c>
-      <c r="H12" s="2" t="n"/>
-      <c r="I12" s="2" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>U.S. Small Cap</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="n">
-        <v>0.01357</v>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>0.022444</v>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>0.028461</v>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>0.032631</v>
-      </c>
-      <c r="G13" s="5" t="n">
-        <v>0.038074</v>
-      </c>
-      <c r="H13" s="2" t="n"/>
-      <c r="I13" s="2" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>International Developed Equity</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="n">
-        <v>0.08142000000000001</v>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>0.134667</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>0.170765</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>0.195788</v>
-      </c>
-      <c r="G14" s="5" t="n">
-        <v>0.228445</v>
-      </c>
-      <c r="H14" s="2" t="n"/>
-      <c r="I14" s="2" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Emerging Markets Equity</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>0.02714</v>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>0.044889</v>
-      </c>
-      <c r="E15" s="5" t="n">
-        <v>0.056922</v>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>0.065263</v>
-      </c>
-      <c r="G15" s="5" t="n">
-        <v>0.07614799999999999</v>
-      </c>
-      <c r="H15" s="2" t="n"/>
-      <c r="I15" s="2" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>U.S. REITs</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Alternatives</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="n">
-        <v>0.005959</v>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>0.000401</v>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>4e-06</v>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>0.02068</v>
-      </c>
-      <c r="G16" s="5" t="n">
-        <v>1.6e-05</v>
-      </c>
-      <c r="H16" s="2" t="n"/>
-      <c r="I16" s="2" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Commodities</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Alternatives</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>0.005959</v>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>0.000401</v>
-      </c>
-      <c r="E17" s="5" t="n">
-        <v>4e-06</v>
-      </c>
-      <c r="F17" s="5" t="n">
-        <v>0.02068</v>
-      </c>
-      <c r="G17" s="5" t="n">
-        <v>1.6e-05</v>
-      </c>
-      <c r="H17" s="2" t="n"/>
-      <c r="I17" s="2" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Income U.S. - U.S. Treasury</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Fixed Income</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="n">
-        <v>0.209977</v>
-      </c>
-      <c r="D18" s="5" t="n">
-        <v>0.136224</v>
-      </c>
-      <c r="E18" s="5" t="n">
-        <v>0.083958</v>
-      </c>
-      <c r="F18" s="5" t="n">
-        <v>0.033658</v>
-      </c>
-      <c r="G18" s="5" t="n">
-        <v>1.3e-05</v>
-      </c>
-      <c r="H18" s="2" t="n"/>
-      <c r="I18" s="2" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Income U.S. Government Related</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Fixed Income</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="n">
-        <v>0.163315</v>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>0.105952</v>
-      </c>
-      <c r="E19" s="5" t="n">
-        <v>0.065301</v>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>0.026179</v>
-      </c>
-      <c r="G19" s="5" t="n">
-        <v>1e-05</v>
-      </c>
-      <c r="H19" s="2" t="n"/>
-      <c r="I19" s="2" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Income U.S. Corporate</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Fixed Income</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="n">
-        <v>0.186646</v>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>0.121088</v>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>0.07463</v>
-      </c>
-      <c r="F20" s="5" t="n">
-        <v>0.029919</v>
-      </c>
-      <c r="G20" s="5" t="n">
-        <v>1.1e-05</v>
-      </c>
-      <c r="H20" s="2" t="n"/>
-      <c r="I20" s="2" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Income U.S. Securitized</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Fixed Income</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="n">
-        <v>0.013998</v>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>0.009082</v>
-      </c>
-      <c r="E21" s="5" t="n">
-        <v>0.005597</v>
-      </c>
-      <c r="F21" s="5" t="n">
-        <v>0.002244</v>
-      </c>
-      <c r="G21" s="5" t="n">
-        <v>1e-06</v>
-      </c>
-      <c r="H21" s="2" t="n"/>
-      <c r="I21" s="2" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Fixed Income International</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Fixed Income</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="n">
-        <v>0.046661</v>
-      </c>
-      <c r="D22" s="5" t="n">
-        <v>0.030272</v>
-      </c>
-      <c r="E22" s="5" t="n">
-        <v>0.018657</v>
-      </c>
-      <c r="F22" s="5" t="n">
-        <v>0.00748</v>
-      </c>
-      <c r="G22" s="5" t="n">
-        <v>3e-06</v>
-      </c>
-      <c r="H22" s="2" t="n"/>
-      <c r="I22" s="2" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Other Fixed Income</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Fixed Income</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="n">
-        <v>0.004666</v>
-      </c>
-      <c r="D23" s="5" t="n">
-        <v>0.003027</v>
-      </c>
-      <c r="E23" s="5" t="n">
-        <v>0.001866</v>
-      </c>
-      <c r="F23" s="5" t="n">
-        <v>0.000748</v>
-      </c>
-      <c r="G23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="2" t="n"/>
-      <c r="I23" s="2" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Cash</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Cash</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="D24" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="E24" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="F24" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G24" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="H24" s="2" t="n"/>
-      <c r="I24" s="2" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4028,13 +2547,13 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>0.006033</v>
+        <v>0.010611</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>0.07529</v>
+        <v>0.074644</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>-0.331615</v>
+        <v>-0.273156</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>0.3</v>
@@ -4049,10 +2568,10 @@
         <v>0.01</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>0.07200000000000001</v>
+        <v>0.07332472972620824</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>0.08200000000000002</v>
+        <v>0.08332472972620825</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
@@ -4067,13 +2586,13 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>-0.002061</v>
+        <v>0.002659</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>0.105505</v>
+        <v>0.105447</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>-0.313364</v>
+        <v>-0.268766</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>0.55</v>
@@ -4088,10 +2607,10 @@
         <v>0.01</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>0.1</v>
+        <v>0.1054471964394289</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>0.11</v>
+        <v>0.1154471964394289</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
@@ -4106,19 +2625,19 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>-0.007287</v>
+        <v>-0.00108</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>0.127</v>
+        <v>0.123065</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>-0.301476</v>
+        <v>-0.260676</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.7114200000000001</v>
+        <v>0.65</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.27858</v>
+        <v>0.34</v>
       </c>
       <c r="G5" s="5" t="n">
         <v>0</v>
@@ -4127,10 +2646,10 @@
         <v>0.01</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>0.127</v>
+        <v>0.1230651077209465</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>0.133</v>
+        <v>0.1290651077209465</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
@@ -4145,35 +2664,35 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>-0.013611</v>
+        <v>-0.00588</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>0.149472</v>
+        <v>0.137783</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>-0.298454</v>
+        <v>-0.26767</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.85</v>
+        <v>0.750985</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.1</v>
+        <v>0.239015</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="H6" s="5" t="n">
         <v>0.01</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>0.153</v>
+        <v>0.1377832186992815</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>0.163</v>
+        <v>0.1477832186992815</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Below target</t>
+          <t>In target</t>
         </is>
       </c>
     </row>
@@ -4184,19 +2703,19 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>-0.016307</v>
+        <v>-0.013175</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0.165737</v>
+        <v>0.157688</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>-0.285433</v>
+        <v>-0.28014</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.99</v>
+        <v>0.90843</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0</v>
+        <v>0.08157</v>
       </c>
       <c r="G7" s="5" t="n">
         <v>0</v>
@@ -4205,14 +2724,14 @@
         <v>0.01</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>0.18</v>
+        <v>0.1576876655884257</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>0.19</v>
+        <v>0.1676876655884257</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Below target</t>
+          <t>In target</t>
         </is>
       </c>
     </row>
@@ -4323,19 +2842,19 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>0.055149</v>
+        <v>0.05756</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>0.082</v>
+        <v>0.083325</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>0.294498</v>
+        <v>0.318757</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0.359831</v>
+        <v>0.302111</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.630169</v>
+        <v>0.687889</v>
       </c>
       <c r="G12" s="5" t="n">
         <v>0</v>
@@ -4344,10 +2863,10 @@
         <v>0.01</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.07200000000000001</v>
+        <v>0.07332472972620824</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0.08200000000000002</v>
+        <v>0.08332472972620825</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
@@ -4362,19 +2881,19 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>0.06071</v>
+        <v>0.06447</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0.11</v>
+        <v>0.115447</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>0.270088</v>
+        <v>0.289915</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0.584416</v>
+        <v>0.55</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.405584</v>
+        <v>0.44</v>
       </c>
       <c r="G13" s="5" t="n">
         <v>0</v>
@@ -4383,10 +2902,10 @@
         <v>0.01</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>0.1</v>
+        <v>0.1054471964394289</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>0.11</v>
+        <v>0.1154471964394289</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
@@ -4401,19 +2920,19 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>0.06456199999999999</v>
+        <v>0.066319</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>0.130897</v>
+        <v>0.129065</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>0.2564</v>
+        <v>0.27365</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0.74</v>
+        <v>0.65</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.25</v>
+        <v>0.34</v>
       </c>
       <c r="G14" s="5" t="n">
         <v>0</v>
@@ -4422,10 +2941,10 @@
         <v>0.01</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>0.127</v>
+        <v>0.1230651077209465</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>0.133</v>
+        <v>0.1290651077209465</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
@@ -4440,35 +2959,35 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>0.06779</v>
+        <v>0.06858599999999999</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>0.149472</v>
+        <v>0.147783</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>0.246133</v>
+        <v>0.254334</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.85</v>
+        <v>0.817936</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.1</v>
+        <v>0.172064</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="H15" s="5" t="n">
         <v>0.01</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>0.153</v>
+        <v>0.1377832186992815</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>0.163</v>
+        <v>0.1477832186992815</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>Below target</t>
+          <t>In target</t>
         </is>
       </c>
     </row>
@@ -4479,13 +2998,13 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>0.070752</v>
+        <v>0.07063999999999999</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>0.165737</v>
+        <v>0.167147</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>0.239852</v>
+        <v>0.237157</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>0.99</v>
@@ -4500,14 +3019,14 @@
         <v>0.01</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>0.18</v>
+        <v>0.1576876655884257</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>0.19</v>
+        <v>0.1676876655884257</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>Below target</t>
+          <t>In target</t>
         </is>
       </c>
     </row>
@@ -4618,31 +3137,31 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>0.107961</v>
+        <v>0.110039</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>0.082</v>
+        <v>0.083325</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>0.938545</v>
+        <v>0.9485710000000001</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0.311824</v>
+        <v>0.409057</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.598176</v>
+        <v>0.580943</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="H21" s="5" t="n">
         <v>0.01</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>0.07200000000000001</v>
+        <v>0.07332472972620824</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>0.08200000000000002</v>
+        <v>0.08332472972620825</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
@@ -4657,31 +3176,31 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>0.125834</v>
+        <v>0.131815</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>0.11</v>
+        <v>0.115447</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>0.862131</v>
+        <v>0.8732569999999999</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0.55</v>
+        <v>0.64</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.382948</v>
+        <v>0.35</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.057052</v>
+        <v>0</v>
       </c>
       <c r="H22" s="5" t="n">
         <v>0.01</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>0.1</v>
+        <v>0.1054471964394289</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>0.11</v>
+        <v>0.1154471964394289</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
@@ -4696,19 +3215,19 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>0.137337</v>
+        <v>0.13959</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>0.130897</v>
+        <v>0.129065</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>0.812369</v>
+        <v>0.841361</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0.74</v>
+        <v>0.735525</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0.25</v>
+        <v>0.254475</v>
       </c>
       <c r="G23" s="5" t="n">
         <v>0</v>
@@ -4717,10 +3236,10 @@
         <v>0.01</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>0.127</v>
+        <v>0.1230651077209465</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>0.133</v>
+        <v>0.1290651077209465</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
@@ -4735,35 +3254,35 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>0.149191</v>
+        <v>0.149093</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>0.149472</v>
+        <v>0.147783</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>0.79072</v>
+        <v>0.799099</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>0.85</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="H24" s="5" t="n">
         <v>0.01</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>0.153</v>
+        <v>0.1377832186992815</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>0.163</v>
+        <v>0.1477832186992815</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>Below target</t>
+          <t>In target</t>
         </is>
       </c>
     </row>
@@ -4774,13 +3293,13 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>0.157811</v>
+        <v>0.158841</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>0.165737</v>
+        <v>0.167147</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>0.765136</v>
+        <v>0.764844</v>
       </c>
       <c r="E25" s="5" t="n">
         <v>0.99</v>
@@ -4795,14 +3314,14 @@
         <v>0.01</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>0.18</v>
+        <v>0.1576876655884257</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>0.19</v>
+        <v>0.1676876655884257</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>Below target</t>
+          <t>In target</t>
         </is>
       </c>
     </row>
@@ -4816,7 +3335,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4828,8 +3347,8 @@
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
   </cols>
@@ -4889,12 +3408,12 @@
         <v>0.5</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>0.07200000000000001</v>
+        <v>0.07332472972620824</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>0.08200000000000002</v>
-      </c>
-      <c r="G2" s="10" t="inlineStr">
+        <v>0.08332472972620825</v>
+      </c>
+      <c r="G2" s="9" t="inlineStr">
         <is>
           <t>Editable policy band used by optimizer script</t>
         </is>
@@ -4918,12 +3437,12 @@
         <v>0.75</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>0.07200000000000001</v>
+        <v>0.07332472972620824</v>
       </c>
       <c r="F3" s="7" t="n">
-        <v>0.08200000000000002</v>
-      </c>
-      <c r="G3" s="10" t="inlineStr">
+        <v>0.08332472972620825</v>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
         <is>
           <t>Editable policy band used by optimizer script</t>
         </is>
@@ -4944,15 +3463,15 @@
         <v>0</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>0.07200000000000001</v>
+        <v>0.07332472972620824</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>0.08200000000000002</v>
-      </c>
-      <c r="G4" s="10" t="inlineStr">
+        <v>0.08332472972620825</v>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
         <is>
           <t>Editable policy band used by optimizer script</t>
         </is>
@@ -4976,12 +3495,12 @@
         <v>0.01</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>0.07200000000000001</v>
+        <v>0.07332472972620824</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>0.08200000000000002</v>
-      </c>
-      <c r="G5" s="10" t="inlineStr">
+        <v>0.08332472972620825</v>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
         <is>
           <t>Editable policy band used by optimizer script</t>
         </is>
@@ -5005,12 +3524,12 @@
         <v>0.65</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>0.1</v>
+        <v>0.1054471964394289</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="G6" s="10" t="inlineStr">
+        <v>0.1154471964394289</v>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
         <is>
           <t>Editable policy band used by optimizer script</t>
         </is>
@@ -5034,12 +3553,12 @@
         <v>0.55</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>0.1</v>
+        <v>0.1054471964394289</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="G7" s="10" t="inlineStr">
+        <v>0.1154471964394289</v>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
         <is>
           <t>Editable policy band used by optimizer script</t>
         </is>
@@ -5060,15 +3579,15 @@
         <v>0</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>0.1</v>
+        <v>0.1054471964394289</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="G8" s="10" t="inlineStr">
+        <v>0.1154471964394289</v>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
         <is>
           <t>Editable policy band used by optimizer script</t>
         </is>
@@ -5092,12 +3611,12 @@
         <v>0.01</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>0.1</v>
+        <v>0.1054471964394289</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="G9" s="10" t="inlineStr">
+        <v>0.1154471964394289</v>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
         <is>
           <t>Editable policy band used by optimizer script</t>
         </is>
@@ -5121,12 +3640,12 @@
         <v>0.75</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>0.127</v>
+        <v>0.1230651077209465</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="G10" s="10" t="inlineStr">
+        <v>0.1290651077209465</v>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
         <is>
           <t>Editable policy band used by optimizer script</t>
         </is>
@@ -5150,12 +3669,12 @@
         <v>0.4</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>0.127</v>
+        <v>0.1230651077209465</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="G11" s="10" t="inlineStr">
+        <v>0.1290651077209465</v>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
         <is>
           <t>Editable policy band used by optimizer script</t>
         </is>
@@ -5176,15 +3695,15 @@
         <v>0</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>0.127</v>
+        <v>0.1230651077209465</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="G12" s="10" t="inlineStr">
+        <v>0.1290651077209465</v>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
         <is>
           <t>Editable policy band used by optimizer script</t>
         </is>
@@ -5208,12 +3727,12 @@
         <v>0.01</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>0.127</v>
+        <v>0.1230651077209465</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="G13" s="10" t="inlineStr">
+        <v>0.1290651077209465</v>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
         <is>
           <t>Editable policy band used by optimizer script</t>
         </is>
@@ -5237,12 +3756,12 @@
         <v>0.85</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>0.153</v>
+        <v>0.1377832186992815</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>0.163</v>
-      </c>
-      <c r="G14" s="10" t="inlineStr">
+        <v>0.1477832186992815</v>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
         <is>
           <t>Editable policy band used by optimizer script</t>
         </is>
@@ -5266,12 +3785,12 @@
         <v>0.25</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>0.153</v>
+        <v>0.1377832186992815</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>0.163</v>
-      </c>
-      <c r="G15" s="10" t="inlineStr">
+        <v>0.1477832186992815</v>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
         <is>
           <t>Editable policy band used by optimizer script</t>
         </is>
@@ -5292,15 +3811,15 @@
         <v>0</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>0.153</v>
+        <v>0.1377832186992815</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>0.163</v>
-      </c>
-      <c r="G16" s="10" t="inlineStr">
+        <v>0.1477832186992815</v>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
         <is>
           <t>Editable policy band used by optimizer script</t>
         </is>
@@ -5324,12 +3843,12 @@
         <v>0.01</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>0.153</v>
+        <v>0.1377832186992815</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>0.163</v>
-      </c>
-      <c r="G17" s="10" t="inlineStr">
+        <v>0.1477832186992815</v>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
         <is>
           <t>Editable policy band used by optimizer script</t>
         </is>
@@ -5353,12 +3872,12 @@
         <v>1</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>0.18</v>
+        <v>0.1576876655884257</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="G18" s="10" t="inlineStr">
+        <v>0.1676876655884257</v>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
         <is>
           <t>Editable policy band used by optimizer script</t>
         </is>
@@ -5382,12 +3901,12 @@
         <v>0.12</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>0.18</v>
+        <v>0.1576876655884257</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="G19" s="10" t="inlineStr">
+        <v>0.1676876655884257</v>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
         <is>
           <t>Editable policy band used by optimizer script</t>
         </is>
@@ -5408,15 +3927,15 @@
         <v>0</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>0.18</v>
+        <v>0.1576876655884257</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="G20" s="10" t="inlineStr">
+        <v>0.1676876655884257</v>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
         <is>
           <t>Editable policy band used by optimizer script</t>
         </is>
@@ -5440,12 +3959,12 @@
         <v>0.01</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>0.18</v>
+        <v>0.1576876655884257</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="G21" s="10" t="inlineStr">
+        <v>0.1676876655884257</v>
+      </c>
+      <c r="G21" s="9" t="inlineStr">
         <is>
           <t>Editable policy band used by optimizer script</t>
         </is>
@@ -5458,7 +3977,7 @@
       <c r="D22" s="7" t="n"/>
       <c r="E22" s="7" t="n"/>
       <c r="F22" s="7" t="n"/>
-      <c r="G22" s="10" t="n"/>
+      <c r="G22" s="9" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -5478,16 +3997,12 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Pro Rata Mix</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
           <t>Notes</t>
         </is>
       </c>
+      <c r="E23" s="7" t="n"/>
       <c r="F23" s="7" t="n"/>
-      <c r="G23" s="10" t="n"/>
+      <c r="G23" s="9" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5501,16 +4016,14 @@
       <c r="C24" s="7" t="n">
         <v>0.45</v>
       </c>
-      <c r="D24" s="7" t="n">
-        <v>0.4999999999999999</v>
-      </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>Derived from sleeve range midpoints</t>
-        </is>
-      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Direct asset-level bounds used by optimizer</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="n"/>
       <c r="F24" s="7" t="n"/>
-      <c r="G24" s="10" t="n"/>
+      <c r="G24" s="9" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5524,16 +4037,14 @@
       <c r="C25" s="7" t="n">
         <v>0.2</v>
       </c>
-      <c r="D25" s="7" t="n">
-        <v>0.1538461538461538</v>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>Derived from sleeve range midpoints</t>
-        </is>
-      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>Direct asset-level bounds used by optimizer</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="n"/>
       <c r="F25" s="7" t="n"/>
-      <c r="G25" s="10" t="n"/>
+      <c r="G25" s="9" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5547,16 +4058,14 @@
       <c r="C26" s="7" t="n">
         <v>0.05</v>
       </c>
-      <c r="D26" s="7" t="n">
-        <v>0.03846153846153846</v>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>Derived from sleeve range midpoints</t>
-        </is>
-      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Direct asset-level bounds used by optimizer</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="n"/>
       <c r="F26" s="7" t="n"/>
-      <c r="G26" s="10" t="n"/>
+      <c r="G26" s="9" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5570,16 +4079,14 @@
       <c r="C27" s="7" t="n">
         <v>0.2</v>
       </c>
-      <c r="D27" s="7" t="n">
-        <v>0.2307692307692308</v>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>Derived from sleeve range midpoints</t>
-        </is>
-      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>Direct asset-level bounds used by optimizer</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="n"/>
       <c r="F27" s="7" t="n"/>
-      <c r="G27" s="10" t="n"/>
+      <c r="G27" s="9" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5593,16 +4100,14 @@
       <c r="C28" s="7" t="n">
         <v>0.1</v>
       </c>
-      <c r="D28" s="7" t="n">
-        <v>0.07692307692307691</v>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>Derived from sleeve range midpoints</t>
-        </is>
-      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Direct asset-level bounds used by optimizer</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="n"/>
       <c r="F28" s="7" t="n"/>
-      <c r="G28" s="10" t="n"/>
+      <c r="G28" s="9" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5614,18 +4119,16 @@
         <v>0</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="D29" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>Derived from sleeve range midpoints</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>Direct asset-level bounds used by optimizer</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="n"/>
       <c r="F29" s="7" t="n"/>
-      <c r="G29" s="10" t="n"/>
+      <c r="G29" s="9" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5637,18 +4140,16 @@
         <v>0</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="D30" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>Derived from sleeve range midpoints</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>Direct asset-level bounds used by optimizer</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="n"/>
       <c r="F30" s="7" t="n"/>
-      <c r="G30" s="10" t="n"/>
+      <c r="G30" s="9" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -5662,16 +4163,14 @@
       <c r="C31" s="7" t="n">
         <v>0.45</v>
       </c>
-      <c r="D31" s="7" t="n">
-        <v>0.335820895522388</v>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>Derived from sleeve range midpoints</t>
-        </is>
-      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>Direct asset-level bounds used by optimizer</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="n"/>
       <c r="F31" s="7" t="n"/>
-      <c r="G31" s="10" t="n"/>
+      <c r="G31" s="9" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -5685,16 +4184,14 @@
       <c r="C32" s="7" t="n">
         <v>0.35</v>
       </c>
-      <c r="D32" s="7" t="n">
-        <v>0.2611940298507462</v>
-      </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>Derived from sleeve range midpoints</t>
-        </is>
-      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>Direct asset-level bounds used by optimizer</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="n"/>
       <c r="F32" s="7" t="n"/>
-      <c r="G32" s="10" t="n"/>
+      <c r="G32" s="9" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -5708,16 +4205,14 @@
       <c r="C33" s="7" t="n">
         <v>0.4</v>
       </c>
-      <c r="D33" s="7" t="n">
-        <v>0.2985074626865671</v>
-      </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>Derived from sleeve range midpoints</t>
-        </is>
-      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>Direct asset-level bounds used by optimizer</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="n"/>
       <c r="F33" s="7" t="n"/>
-      <c r="G33" s="10" t="n"/>
+      <c r="G33" s="9" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -5731,16 +4226,14 @@
       <c r="C34" s="7" t="n">
         <v>0.03</v>
       </c>
-      <c r="D34" s="7" t="n">
-        <v>0.02238805970149253</v>
-      </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>Derived from sleeve range midpoints</t>
-        </is>
-      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>Direct asset-level bounds used by optimizer</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="n"/>
       <c r="F34" s="7" t="n"/>
-      <c r="G34" s="10" t="n"/>
+      <c r="G34" s="9" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -5754,16 +4247,14 @@
       <c r="C35" s="7" t="n">
         <v>0.1</v>
       </c>
-      <c r="D35" s="7" t="n">
-        <v>0.07462686567164178</v>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>Derived from sleeve range midpoints</t>
-        </is>
-      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>Direct asset-level bounds used by optimizer</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="n"/>
       <c r="F35" s="7" t="n"/>
-      <c r="G35" s="10" t="n"/>
+      <c r="G35" s="9" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -5777,16 +4268,14 @@
       <c r="C36" s="7" t="n">
         <v>0.01</v>
       </c>
-      <c r="D36" s="7" t="n">
-        <v>0.007462686567164177</v>
-      </c>
-      <c r="E36" s="7" t="inlineStr">
-        <is>
-          <t>Derived from sleeve range midpoints</t>
-        </is>
-      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>Direct asset-level bounds used by optimizer</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="n"/>
       <c r="F36" s="7" t="n"/>
-      <c r="G36" s="10" t="n"/>
+      <c r="G36" s="9" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -5800,23 +4289,21 @@
       <c r="C37" s="7" t="n">
         <v>0.01</v>
       </c>
-      <c r="D37" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>Derived from sleeve range midpoints</t>
-        </is>
-      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>Direct asset-level bounds used by optimizer</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="n"/>
       <c r="F37" s="7" t="n"/>
-      <c r="G37" s="10" t="n"/>
+      <c r="G37" s="9" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5877,18 +4364,18 @@
           <t>Conservative MVO weights sum to 100%</t>
         </is>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <f>'MVO Detail'!C17</f>
         <v/>
       </c>
-      <c r="C2" s="11" t="n">
+      <c r="C2" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="11">
+      <c r="D2" s="10">
         <f>B2-C2</f>
         <v/>
       </c>
-      <c r="E2" s="11" t="n">
+      <c r="E2" s="10" t="n">
         <v>0.0001</v>
       </c>
       <c r="F2" s="2">
@@ -5906,18 +4393,18 @@
           <t>Balanced MVO weights sum to 100%</t>
         </is>
       </c>
-      <c r="B3" s="11">
+      <c r="B3" s="10">
         <f>'MVO Detail'!D17</f>
         <v/>
       </c>
-      <c r="C3" s="11" t="n">
+      <c r="C3" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="11">
+      <c r="D3" s="10">
         <f>B3-C3</f>
         <v/>
       </c>
-      <c r="E3" s="11" t="n">
+      <c r="E3" s="10" t="n">
         <v>0.0001</v>
       </c>
       <c r="F3" s="2">
@@ -5935,18 +4422,18 @@
           <t>Moderate MVO weights sum to 100%</t>
         </is>
       </c>
-      <c r="B4" s="11">
+      <c r="B4" s="10">
         <f>'MVO Detail'!E17</f>
         <v/>
       </c>
-      <c r="C4" s="11" t="n">
+      <c r="C4" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="10">
         <f>B4-C4</f>
         <v/>
       </c>
-      <c r="E4" s="11" t="n">
+      <c r="E4" s="10" t="n">
         <v>0.0001</v>
       </c>
       <c r="F4" s="2">
@@ -5964,18 +4451,18 @@
           <t>Growth MVO weights sum to 100%</t>
         </is>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="10">
         <f>'MVO Detail'!F17</f>
         <v/>
       </c>
-      <c r="C5" s="11" t="n">
+      <c r="C5" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="10">
         <f>B5-C5</f>
         <v/>
       </c>
-      <c r="E5" s="11" t="n">
+      <c r="E5" s="10" t="n">
         <v>0.0001</v>
       </c>
       <c r="F5" s="2">
@@ -5993,18 +4480,18 @@
           <t>Aggressive Growth MVO weights sum to 100%</t>
         </is>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="10">
         <f>'MVO Detail'!G17</f>
         <v/>
       </c>
-      <c r="C6" s="11" t="n">
+      <c r="C6" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="10">
         <f>B6-C6</f>
         <v/>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="E6" s="10" t="n">
         <v>0.0001</v>
       </c>
       <c r="F6" s="2">
@@ -6022,18 +4509,18 @@
           <t>Conservative MVO cash equals 1%</t>
         </is>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="10">
         <f>'MVO Detail'!C15</f>
         <v/>
       </c>
-      <c r="C7" s="11" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="D7" s="11">
+      <c r="C7" s="10" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D7" s="10">
         <f>B7-C7</f>
         <v/>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" s="10" t="n">
         <v>0.0001</v>
       </c>
       <c r="F7" s="2">
@@ -6048,18 +4535,18 @@
           <t>Balanced MVO cash equals 1%</t>
         </is>
       </c>
-      <c r="B8" s="11">
+      <c r="B8" s="10">
         <f>'MVO Detail'!D15</f>
         <v/>
       </c>
-      <c r="C8" s="11" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="D8" s="11">
+      <c r="C8" s="10" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D8" s="10">
         <f>B8-C8</f>
         <v/>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="10" t="n">
         <v>0.0001</v>
       </c>
       <c r="F8" s="2">
@@ -6074,18 +4561,18 @@
           <t>Moderate MVO cash equals 1%</t>
         </is>
       </c>
-      <c r="B9" s="11">
+      <c r="B9" s="10">
         <f>'MVO Detail'!E15</f>
         <v/>
       </c>
-      <c r="C9" s="11" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="D9" s="11">
+      <c r="C9" s="10" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D9" s="10">
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="E9" s="10" t="n">
         <v>0.0001</v>
       </c>
       <c r="F9" s="2">
@@ -6100,18 +4587,18 @@
           <t>Growth MVO cash equals 1%</t>
         </is>
       </c>
-      <c r="B10" s="11">
+      <c r="B10" s="10">
         <f>'MVO Detail'!F15</f>
         <v/>
       </c>
-      <c r="C10" s="11" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="D10" s="11">
+      <c r="C10" s="10" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D10" s="10">
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="10" t="n">
         <v>0.0001</v>
       </c>
       <c r="F10" s="2">
@@ -6126,18 +4613,18 @@
           <t>Aggressive Growth MVO cash equals 1%</t>
         </is>
       </c>
-      <c r="B11" s="11">
+      <c r="B11" s="10">
         <f>'MVO Detail'!G15</f>
         <v/>
       </c>
-      <c r="C11" s="11" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="D11" s="11">
+      <c r="C11" s="10" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D11" s="10">
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="11" t="n">
+      <c r="E11" s="10" t="n">
         <v>0.0001</v>
       </c>
       <c r="F11" s="2">
@@ -6152,18 +4639,18 @@
           <t>All MVO sub-weights are non-negative</t>
         </is>
       </c>
-      <c r="B12" s="11">
+      <c r="B12" s="10">
         <f>MIN('MVO Detail'!C2:G16)</f>
         <v/>
       </c>
-      <c r="C12" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="11">
+      <c r="C12" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="10">
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="11" t="n">
+      <c r="E12" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="2">
@@ -6177,13 +4664,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -6209,7 +4696,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>Source file</t>
         </is>
@@ -6279,66 +4766,83 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Five portfolios</t>
+          <t>Monte Carlo</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Category bands and target volatility ranges are explicit on Constraints tab; cash is hard-coded with both minimum and maximum at 1% in every model.</t>
+          <t>Removed from all calculations for now.</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Approve or revise the equity/fixed income/alternatives policy bands and target volatility bands.</t>
+          <t>Redesign simulation methodology before adding it back.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Tax/location</t>
+          <t>Five portfolios</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Not modeled.</t>
+          <t>Category bands and target volatility ranges are explicit on Constraints tab; cash is hard-coded with both minimum and maximum at 1% in every model.</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Decide taxable vs qualified account treatment, muni bond role, and tax-aware placement.</t>
+          <t>Approve or revise the equity/fixed income/alternatives policy bands and target volatility bands.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Liquidity/implementation</t>
+          <t>Tax/location</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>No ETF/mutual fund tickers selected yet.</t>
+          <t>Not modeled.</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Map each style sleeve to actual funds and expense ratios.</t>
+          <t>Decide taxable vs qualified account treatment, muni bond role, and tax-aware placement.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>Liquidity/implementation</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>No ETF/mutual fund tickers selected yet.</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Map each style sleeve to actual funds and expense ratios.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
           <t>Rebalancing</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Not modeled.</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Choose annual, semiannual, or tolerance-band rebalancing.</t>
         </is>

--- a/outputs/paul_asset_allocation_model.xlsx
+++ b/outputs/paul_asset_allocation_model.xlsx
@@ -939,19 +939,19 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>0.05756</v>
+        <v>0.05748</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>0.083325</v>
+        <v>0.083052</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>0.318757</v>
+        <v>0.318835</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.302111</v>
+        <v>0.300114</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.687889</v>
+        <v>0.689886</v>
       </c>
       <c r="G11" s="5" t="n">
         <v>0</v>
@@ -960,10 +960,10 @@
         <v>0.01</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0.07332472972620824</v>
+        <v>0.07305185153905434</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>0.08332472972620825</v>
+        <v>0.08305185153905435</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
@@ -978,19 +978,19 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>0.06447</v>
+        <v>0.065857</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>0.115447</v>
+        <v>0.113714</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>0.289915</v>
+        <v>0.306534</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0.55</v>
+        <v>0.570027</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.44</v>
+        <v>0.419973</v>
       </c>
       <c r="G12" s="5" t="n">
         <v>0</v>
@@ -999,10 +999,10 @@
         <v>0.01</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.1054471964394289</v>
+        <v>0.1037143091201067</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0.1154471964394289</v>
+        <v>0.1137143091201067</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
@@ -1017,19 +1017,19 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>0.066319</v>
+        <v>0.068508</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0.129065</v>
+        <v>0.126688</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>0.27365</v>
+        <v>0.296068</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0.65</v>
+        <v>0.69333</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.34</v>
+        <v>0.29667</v>
       </c>
       <c r="G13" s="5" t="n">
         <v>0</v>
@@ -1038,10 +1038,10 @@
         <v>0.01</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>0.1230651077209465</v>
+        <v>0.1206880986447292</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>0.1290651077209465</v>
+        <v>0.1266880986447292</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
@@ -1056,19 +1056,19 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>0.06858599999999999</v>
+        <v>0.071757</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>0.147783</v>
+        <v>0.14506</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>0.254334</v>
+        <v>0.280964</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0.817936</v>
+        <v>0.828889</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.172064</v>
+        <v>0.161111</v>
       </c>
       <c r="G14" s="5" t="n">
         <v>0</v>
@@ -1077,10 +1077,10 @@
         <v>0.01</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>0.1377832186992815</v>
+        <v>0.1350603109512361</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>0.1477832186992815</v>
+        <v>0.1450603109512361</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
@@ -1095,13 +1095,13 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>0.07063999999999999</v>
+        <v>0.07421</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>0.167147</v>
+        <v>0.164487</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>0.237157</v>
+        <v>0.262695</v>
       </c>
       <c r="E15" s="5" t="n">
         <v>0.99</v>
@@ -1116,10 +1116,10 @@
         <v>0.01</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>0.1576876655884257</v>
+        <v>0.1560336873549507</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>0.1676876655884257</v>
+        <v>0.1660336873549507</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
@@ -1234,19 +1234,19 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>0.05756</v>
+        <v>0.05748</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>0.083325</v>
+        <v>0.083052</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>0.318757</v>
+        <v>0.318835</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0.302111</v>
+        <v>0.300114</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0.687889</v>
+        <v>0.689886</v>
       </c>
       <c r="G20" s="5" t="n">
         <v>0</v>
@@ -1255,10 +1255,10 @@
         <v>0.01</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>0.07332472972620824</v>
+        <v>0.07305185153905434</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>0.08332472972620825</v>
+        <v>0.08305185153905435</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
@@ -1273,19 +1273,19 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>0.06447</v>
+        <v>0.065857</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>0.115447</v>
+        <v>0.113714</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>0.289915</v>
+        <v>0.306534</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0.55</v>
+        <v>0.570027</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.44</v>
+        <v>0.419973</v>
       </c>
       <c r="G21" s="5" t="n">
         <v>0</v>
@@ -1294,10 +1294,10 @@
         <v>0.01</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>0.1054471964394289</v>
+        <v>0.1037143091201067</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>0.1154471964394289</v>
+        <v>0.1137143091201067</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
@@ -1312,19 +1312,19 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>0.066319</v>
+        <v>0.068508</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>0.129065</v>
+        <v>0.126688</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>0.27365</v>
+        <v>0.296068</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0.65</v>
+        <v>0.69333</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.34</v>
+        <v>0.29667</v>
       </c>
       <c r="G22" s="5" t="n">
         <v>0</v>
@@ -1333,10 +1333,10 @@
         <v>0.01</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>0.1230651077209465</v>
+        <v>0.1206880986447292</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>0.1290651077209465</v>
+        <v>0.1266880986447292</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
@@ -1351,19 +1351,19 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>0.06858599999999999</v>
+        <v>0.071757</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>0.147783</v>
+        <v>0.14506</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>0.254334</v>
+        <v>0.280964</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0.817936</v>
+        <v>0.828889</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0.172064</v>
+        <v>0.161111</v>
       </c>
       <c r="G23" s="5" t="n">
         <v>0</v>
@@ -1372,10 +1372,10 @@
         <v>0.01</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>0.1377832186992815</v>
+        <v>0.1350603109512361</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>0.1477832186992815</v>
+        <v>0.1450603109512361</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
@@ -1390,13 +1390,13 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>0.07063999999999999</v>
+        <v>0.07421</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>0.167147</v>
+        <v>0.164487</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>0.237157</v>
+        <v>0.262695</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>0.99</v>
@@ -1411,10 +1411,10 @@
         <v>0.01</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>0.1576876655884257</v>
+        <v>0.1560336873549507</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>0.1676876655884257</v>
+        <v>0.1660336873549507</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1598,7 +1598,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>International Developed Equity</t>
+          <t>U.S. Value</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -1608,31 +1608,31 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>EAFE Equity</t>
+          <t>U.S. Equity Value Factor</t>
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>0.081</v>
+        <v>0.077</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>0.1762945661402543</v>
+        <v>0.1770047690845011</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>0.2</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>EAFE Equity</t>
+          <t>U.S. Equity Value Factor</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Emerging Markets Equity</t>
+          <t>U.S. Growth</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -1642,235 +1642,235 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Emerging Markets Equity</t>
+          <t>U.S. Large Cap</t>
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.067</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>0.2093318280359241</v>
+        <v>0.1647014248435096</v>
       </c>
       <c r="F6" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Emerging Markets Equity</t>
+          <t>Correlation proxy: U.S. Large Cap</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>U.S. REITs</t>
+          <t>U.S. Income</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Alternatives</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>U.S. REITs</t>
+          <t>U.S. Equity Dividend Yield Factor</t>
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>0.08</v>
+        <v>0.077</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>0.1739687863508271</v>
+        <v>0.1635694336476759</v>
       </c>
       <c r="F7" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>U.S. REITs</t>
+          <t>U.S. Equity Dividend Yield Factor</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>U.S. Quality</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Alternatives</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>U.S. Equity Quality Factor</t>
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>0.038</v>
+        <v>0.067</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>0.1831843108236745</v>
+        <v>0.1510761822764584</v>
       </c>
       <c r="F8" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>U.S. Equity Quality Factor</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Income U.S. - U.S. Treasury</t>
+          <t>International Developed Equity</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Fixed Income</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>U.S. Intermediate Treasuries, U.S. Long Treasuries, TIPS</t>
+          <t>EAFE Equity</t>
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>0.04066666666666666</v>
+        <v>0.081</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>0.06760238506172241</v>
+        <v>0.1762945661402543</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>0.45</v>
+        <v>0.2</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Equal-weight U.S. Intermediate Treasuries, U.S. Long Treasuries, and TIPS</t>
+          <t>EAFE Equity</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Income U.S. Government Related</t>
+          <t>Emerging Markets Equity</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Fixed Income</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>U.S. Aggregate Bonds, U.S. Muni 1-15 Yr Blend</t>
+          <t>Emerging Markets Equity</t>
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>0.04099999999999999</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>0.04155805259925415</v>
+        <v>0.2093318280359241</v>
       </c>
       <c r="F10" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>0.35</v>
+        <v>0.1</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Equal-weight U.S. Aggregate Bonds and U.S. Muni 1-15 Yr Blend</t>
+          <t>Emerging Markets Equity</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Income U.S. Corporate</t>
+          <t>U.S. REITs</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Fixed Income</t>
+          <t>Alternatives</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>U.S. Inv Grade Corporate Bonds, U.S. High Yield Bonds</t>
+          <t>U.S. REITs</t>
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.0555</v>
+        <v>0.08</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>0.07371002061513575</v>
+        <v>0.1739687863508271</v>
       </c>
       <c r="F11" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Equal-weight U.S. Investment Grade Corporate Bonds and U.S. High Yield Bonds</t>
+          <t>U.S. REITs</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Income U.S. Securitized</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Fixed Income</t>
+          <t>Alternatives</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>U.S. Securitized</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.049</v>
+        <v>0.038</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>0.04185940438750216</v>
+        <v>0.1831843108236745</v>
       </c>
       <c r="F12" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>U.S. Securitized</t>
+          <t>Commodities</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Fixed Income International</t>
+          <t>Income U.S. - U.S. Treasury</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1880,31 +1880,31 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>World ex-U.S. Government Bonds hedged, Emerging Markets Sovereign Debt, Emerging Markets Corporate Bonds</t>
+          <t>U.S. Intermediate Treasuries, U.S. Long Treasuries, TIPS</t>
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.05266666666666667</v>
+        <v>0.04066666666666666</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>0.06020932811355845</v>
+        <v>0.06760238506172241</v>
       </c>
       <c r="F13" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>0.1</v>
+        <v>0.45</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Equal-weight World ex-U.S. Government Bonds hedged, Emerging Markets Sovereign Debt, and Emerging Markets Corporate Bonds</t>
+          <t>Equal-weight U.S. Intermediate Treasuries, U.S. Long Treasuries, and TIPS</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Other Fixed Income</t>
+          <t>Income U.S. Government Related</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1914,56 +1914,192 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>U.S. Leveraged Loans, Emerging Markets Local Currency Debt, U.S. Muni High Yield</t>
+          <t>U.S. Aggregate Bonds, U.S. Muni 1-15 Yr Blend</t>
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.058</v>
+        <v>0.04099999999999999</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>0.0731350475003347</v>
+        <v>0.04155805259925415</v>
       </c>
       <c r="F14" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>0.01</v>
+        <v>0.35</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Equal-weight U.S. Leveraged Loans, Emerging Markets Local Currency Debt, and U.S. Muni High Yield</t>
+          <t>Equal-weight U.S. Aggregate Bonds and U.S. Muni 1-15 Yr Blend</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>Income U.S. Corporate</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Fixed Income</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>U.S. Inv Grade Corporate Bonds, U.S. High Yield Bonds</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>0.0555</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>0.07371002061513575</v>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Equal-weight U.S. Investment Grade Corporate Bonds and U.S. High Yield Bonds</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Income U.S. Securitized</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Fixed Income</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>U.S. Securitized</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>0.04185940438750216</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>U.S. Securitized</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Fixed Income International</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Fixed Income</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>World ex-U.S. Government Bonds hedged, Emerging Markets Sovereign Debt, Emerging Markets Corporate Bonds</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>0.05266666666666667</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>0.06020932811355845</v>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Equal-weight World ex-U.S. Government Bonds hedged, Emerging Markets Sovereign Debt, and Emerging Markets Corporate Bonds</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Other Fixed Income</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Fixed Income</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>U.S. Leveraged Loans, Emerging Markets Local Currency Debt, U.S. Muni High Yield</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>0.0731350475003347</v>
+      </c>
+      <c r="F18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Equal-weight U.S. Leveraged Loans, Emerging Markets Local Currency Debt, and U.S. Muni High Yield</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
           <t>Cash</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Cash</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>U.S. Cash</t>
         </is>
       </c>
-      <c r="D15" s="7" t="n">
+      <c r="D19" s="7" t="n">
         <v>0.031</v>
       </c>
-      <c r="E15" s="7" t="n">
+      <c r="E19" s="7" t="n">
         <v>0.006692990421794862</v>
       </c>
-      <c r="F15" s="7" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G15" s="7" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="F19" s="7" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>U.S. Cash</t>
         </is>
@@ -1980,7 +2116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -2044,16 +2180,16 @@
         <v>0.2</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>0.239219</v>
+        <v>0.2</v>
       </c>
       <c r="E2" s="5" t="n">
         <v>0.2</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>0.317936</v>
+        <v>0.2</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.44</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="3">
@@ -2071,16 +2207,16 @@
         <v>0</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>0.02115</v>
+        <v>0</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.2</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="4">
@@ -2107,13 +2243,13 @@
         <v>0</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>International Developed Equity</t>
+          <t>U.S. Value</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -2122,13 +2258,13 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>0.102111</v>
+        <v>0</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.2</v>
+        <v>0.09333</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0.2</v>
@@ -2140,7 +2276,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Emerging Markets Equity</t>
+          <t>U.S. Growth</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -2152,54 +2288,54 @@
         <v>0</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>0.089631</v>
+        <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>U.S. REITs</t>
+          <t>U.S. Income</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Alternatives</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0</v>
+        <v>0.000114</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>0</v>
+        <v>0.170027</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>U.S. Quality</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Alternatives</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
@@ -2221,43 +2357,43 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Income U.S. - U.S. Treasury</t>
+          <t>International Developed Equity</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Fixed Income</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0.002264</v>
+        <v>0.1</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Income U.S. Government Related</t>
+          <t>Emerging Markets Equity</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Fixed Income</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>0.145625</v>
+        <v>0</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>0</v>
@@ -2266,34 +2402,34 @@
         <v>0</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0</v>
+        <v>0.028889</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Income U.S. Corporate</t>
+          <t>U.S. REITs</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Fixed Income</t>
+          <t>Alternatives</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>0.311147</v>
+        <v>0</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.301335</v>
+        <v>0</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.162064</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5" t="n">
         <v>0</v>
@@ -2302,22 +2438,22 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Income U.S. Securitized</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Fixed Income</t>
+          <t>Alternatives</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0.028665</v>
+        <v>0</v>
       </c>
       <c r="F12" s="5" t="n">
         <v>0</v>
@@ -2329,7 +2465,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Fixed Income International</t>
+          <t>Income U.S. - U.S. Treasury</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -2338,10 +2474,10 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0.1</v>
+        <v>0.002832</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>0.088853</v>
+        <v>0</v>
       </c>
       <c r="E13" s="5" t="n">
         <v>0</v>
@@ -2356,7 +2492,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Other Fixed Income</t>
+          <t>Income U.S. Government Related</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -2365,16 +2501,16 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>0.01</v>
+        <v>0.147054</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="G14" s="5" t="n">
         <v>0</v>
@@ -2383,59 +2519,167 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Income U.S. Corporate</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Fixed Income</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>0.01</v>
+        <v>0.4</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>0.01</v>
+        <v>0.279973</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.01</v>
+        <v>0.15667</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.01</v>
+        <v>0.151111</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>Income U.S. Securitized</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Fixed Income</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Fixed Income International</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Fixed Income</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Other Fixed Income</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Fixed Income</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="C16" s="8">
-        <f>SUM(C2:C15)</f>
+      <c r="C20" s="8">
+        <f>SUM(C2:C19)</f>
         <v/>
       </c>
-      <c r="D16" s="8">
-        <f>SUM(D2:D15)</f>
+      <c r="D20" s="8">
+        <f>SUM(D2:D19)</f>
         <v/>
       </c>
-      <c r="E16" s="8">
-        <f>SUM(E2:E15)</f>
+      <c r="E20" s="8">
+        <f>SUM(E2:E19)</f>
         <v/>
       </c>
-      <c r="F16" s="8">
-        <f>SUM(F2:F15)</f>
+      <c r="F20" s="8">
+        <f>SUM(F2:F19)</f>
         <v/>
       </c>
-      <c r="G16" s="8">
-        <f>SUM(G2:G15)</f>
+      <c r="G20" s="8">
+        <f>SUM(G2:G19)</f>
         <v/>
       </c>
     </row>
@@ -2568,10 +2812,10 @@
         <v>0.01</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>0.07332472972620824</v>
+        <v>0.07305185153905434</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>0.08332472972620825</v>
+        <v>0.08305185153905435</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
@@ -2586,13 +2830,13 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>0.002659</v>
+        <v>0.004365</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>0.105447</v>
+        <v>0.103714</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>-0.268766</v>
+        <v>-0.256814</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>0.55</v>
@@ -2607,10 +2851,10 @@
         <v>0.01</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>0.1054471964394289</v>
+        <v>0.1037143091201067</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>0.1154471964394289</v>
+        <v>0.1137143091201067</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
@@ -2625,13 +2869,13 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>-0.00108</v>
+        <v>0.001432</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>0.123065</v>
+        <v>0.120688</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>-0.260676</v>
+        <v>-0.244997</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>0.65</v>
@@ -2646,10 +2890,10 @@
         <v>0.01</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>0.1230651077209465</v>
+        <v>0.1206880986447292</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>0.1290651077209465</v>
+        <v>0.1266880986447292</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
@@ -2664,19 +2908,19 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>-0.00588</v>
+        <v>-0.002169</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>0.137783</v>
+        <v>0.13506</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>-0.26767</v>
+        <v>-0.245587</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.750985</v>
+        <v>0.75</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.239015</v>
+        <v>0.24</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>0</v>
@@ -2685,10 +2929,10 @@
         <v>0.01</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>0.1377832186992815</v>
+        <v>0.1350603109512361</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>0.1477832186992815</v>
+        <v>0.1450603109512361</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
@@ -2703,19 +2947,19 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>-0.013175</v>
+        <v>-0.008129000000000001</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0.157688</v>
+        <v>0.156034</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>-0.28014</v>
+        <v>-0.25077</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.90843</v>
+        <v>0.95519</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.08157</v>
+        <v>0.03481</v>
       </c>
       <c r="G7" s="5" t="n">
         <v>0</v>
@@ -2724,10 +2968,10 @@
         <v>0.01</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>0.1576876655884257</v>
+        <v>0.1560336873549507</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>0.1676876655884257</v>
+        <v>0.1660336873549507</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
@@ -2842,19 +3086,19 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>0.05756</v>
+        <v>0.05748</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>0.083325</v>
+        <v>0.083052</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>0.318757</v>
+        <v>0.318835</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0.302111</v>
+        <v>0.300114</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.687889</v>
+        <v>0.689886</v>
       </c>
       <c r="G12" s="5" t="n">
         <v>0</v>
@@ -2863,10 +3107,10 @@
         <v>0.01</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.07332472972620824</v>
+        <v>0.07305185153905434</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0.08332472972620825</v>
+        <v>0.08305185153905435</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
@@ -2881,19 +3125,19 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>0.06447</v>
+        <v>0.065857</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0.115447</v>
+        <v>0.113714</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>0.289915</v>
+        <v>0.306534</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0.55</v>
+        <v>0.570027</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.44</v>
+        <v>0.419973</v>
       </c>
       <c r="G13" s="5" t="n">
         <v>0</v>
@@ -2902,10 +3146,10 @@
         <v>0.01</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>0.1054471964394289</v>
+        <v>0.1037143091201067</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>0.1154471964394289</v>
+        <v>0.1137143091201067</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
@@ -2920,19 +3164,19 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>0.066319</v>
+        <v>0.068508</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>0.129065</v>
+        <v>0.126688</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>0.27365</v>
+        <v>0.296068</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0.65</v>
+        <v>0.69333</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.34</v>
+        <v>0.29667</v>
       </c>
       <c r="G14" s="5" t="n">
         <v>0</v>
@@ -2941,10 +3185,10 @@
         <v>0.01</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>0.1230651077209465</v>
+        <v>0.1206880986447292</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>0.1290651077209465</v>
+        <v>0.1266880986447292</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
@@ -2959,19 +3203,19 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>0.06858599999999999</v>
+        <v>0.071757</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>0.147783</v>
+        <v>0.14506</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>0.254334</v>
+        <v>0.280964</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.817936</v>
+        <v>0.828889</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.172064</v>
+        <v>0.161111</v>
       </c>
       <c r="G15" s="5" t="n">
         <v>0</v>
@@ -2980,10 +3224,10 @@
         <v>0.01</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>0.1377832186992815</v>
+        <v>0.1350603109512361</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>0.1477832186992815</v>
+        <v>0.1450603109512361</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
@@ -2998,13 +3242,13 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>0.07063999999999999</v>
+        <v>0.07421</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>0.167147</v>
+        <v>0.164487</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>0.237157</v>
+        <v>0.262695</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>0.99</v>
@@ -3019,10 +3263,10 @@
         <v>0.01</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>0.1576876655884257</v>
+        <v>0.1560336873549507</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>0.1676876655884257</v>
+        <v>0.1660336873549507</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
@@ -3137,19 +3381,19 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>0.110039</v>
+        <v>0.110162</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>0.083325</v>
+        <v>0.083052</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>0.9485710000000001</v>
+        <v>0.953166</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0.409057</v>
+        <v>0.422974</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.580943</v>
+        <v>0.567026</v>
       </c>
       <c r="G21" s="5" t="n">
         <v>0</v>
@@ -3158,10 +3402,10 @@
         <v>0.01</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>0.07332472972620824</v>
+        <v>0.07305185153905434</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>0.08332472972620825</v>
+        <v>0.08305185153905435</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
@@ -3176,13 +3420,13 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>0.131815</v>
+        <v>0.131705</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>0.115447</v>
+        <v>0.113714</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>0.8732569999999999</v>
+        <v>0.885598</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>0.64</v>
@@ -3197,10 +3441,10 @@
         <v>0.01</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>0.1054471964394289</v>
+        <v>0.1037143091201067</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>0.1154471964394289</v>
+        <v>0.1137143091201067</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
@@ -3215,19 +3459,19 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>0.13959</v>
+        <v>0.140011</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>0.129065</v>
+        <v>0.126688</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>0.841361</v>
+        <v>0.860466</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0.735525</v>
+        <v>0.74</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0.254475</v>
+        <v>0.25</v>
       </c>
       <c r="G23" s="5" t="n">
         <v>0</v>
@@ -3236,10 +3480,10 @@
         <v>0.01</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>0.1230651077209465</v>
+        <v>0.1206880986447292</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>0.1290651077209465</v>
+        <v>0.1266880986447292</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
@@ -3254,13 +3498,13 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>0.149093</v>
+        <v>0.150475</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>0.147783</v>
+        <v>0.14506</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>0.799099</v>
+        <v>0.823622</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>0.85</v>
@@ -3275,10 +3519,10 @@
         <v>0.01</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>0.1377832186992815</v>
+        <v>0.1350603109512361</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>0.1477832186992815</v>
+        <v>0.1450603109512361</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
@@ -3293,13 +3537,13 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>0.158841</v>
+        <v>0.16197</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>0.167147</v>
+        <v>0.166034</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>0.764844</v>
+        <v>0.788813</v>
       </c>
       <c r="E25" s="5" t="n">
         <v>0.99</v>
@@ -3314,10 +3558,10 @@
         <v>0.01</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>0.1576876655884257</v>
+        <v>0.1560336873549507</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>0.1676876655884257</v>
+        <v>0.1660336873549507</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
@@ -3341,7 +3585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3408,10 +3652,10 @@
         <v>0.5</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>0.07332472972620824</v>
+        <v>0.07305185153905434</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>0.08332472972620825</v>
+        <v>0.08305185153905435</v>
       </c>
       <c r="G2" s="9" t="inlineStr">
         <is>
@@ -3437,10 +3681,10 @@
         <v>0.75</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>0.07332472972620824</v>
+        <v>0.07305185153905434</v>
       </c>
       <c r="F3" s="7" t="n">
-        <v>0.08332472972620825</v>
+        <v>0.08305185153905435</v>
       </c>
       <c r="G3" s="9" t="inlineStr">
         <is>
@@ -3466,10 +3710,10 @@
         <v>0</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>0.07332472972620824</v>
+        <v>0.07305185153905434</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>0.08332472972620825</v>
+        <v>0.08305185153905435</v>
       </c>
       <c r="G4" s="9" t="inlineStr">
         <is>
@@ -3495,10 +3739,10 @@
         <v>0.01</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>0.07332472972620824</v>
+        <v>0.07305185153905434</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>0.08332472972620825</v>
+        <v>0.08305185153905435</v>
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
@@ -3524,10 +3768,10 @@
         <v>0.65</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>0.1054471964394289</v>
+        <v>0.1037143091201067</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>0.1154471964394289</v>
+        <v>0.1137143091201067</v>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
@@ -3553,10 +3797,10 @@
         <v>0.55</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>0.1054471964394289</v>
+        <v>0.1037143091201067</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>0.1154471964394289</v>
+        <v>0.1137143091201067</v>
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
@@ -3582,10 +3826,10 @@
         <v>0</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>0.1054471964394289</v>
+        <v>0.1037143091201067</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>0.1154471964394289</v>
+        <v>0.1137143091201067</v>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
@@ -3611,10 +3855,10 @@
         <v>0.01</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>0.1054471964394289</v>
+        <v>0.1037143091201067</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>0.1154471964394289</v>
+        <v>0.1137143091201067</v>
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
@@ -3640,10 +3884,10 @@
         <v>0.75</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>0.1230651077209465</v>
+        <v>0.1206880986447292</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>0.1290651077209465</v>
+        <v>0.1266880986447292</v>
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
@@ -3669,10 +3913,10 @@
         <v>0.4</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>0.1230651077209465</v>
+        <v>0.1206880986447292</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>0.1290651077209465</v>
+        <v>0.1266880986447292</v>
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
@@ -3698,10 +3942,10 @@
         <v>0</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>0.1230651077209465</v>
+        <v>0.1206880986447292</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>0.1290651077209465</v>
+        <v>0.1266880986447292</v>
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
@@ -3727,10 +3971,10 @@
         <v>0.01</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>0.1230651077209465</v>
+        <v>0.1206880986447292</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>0.1290651077209465</v>
+        <v>0.1266880986447292</v>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
@@ -3756,10 +4000,10 @@
         <v>0.85</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>0.1377832186992815</v>
+        <v>0.1350603109512361</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>0.1477832186992815</v>
+        <v>0.1450603109512361</v>
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
@@ -3785,10 +4029,10 @@
         <v>0.25</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>0.1377832186992815</v>
+        <v>0.1350603109512361</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>0.1477832186992815</v>
+        <v>0.1450603109512361</v>
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
@@ -3814,10 +4058,10 @@
         <v>0</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>0.1377832186992815</v>
+        <v>0.1350603109512361</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>0.1477832186992815</v>
+        <v>0.1450603109512361</v>
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
@@ -3843,10 +4087,10 @@
         <v>0.01</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>0.1377832186992815</v>
+        <v>0.1350603109512361</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>0.1477832186992815</v>
+        <v>0.1450603109512361</v>
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
@@ -3872,10 +4116,10 @@
         <v>1</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>0.1576876655884257</v>
+        <v>0.1560336873549507</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>0.1676876655884257</v>
+        <v>0.1660336873549507</v>
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
@@ -3901,10 +4145,10 @@
         <v>0.12</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>0.1576876655884257</v>
+        <v>0.1560336873549507</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>0.1676876655884257</v>
+        <v>0.1660336873549507</v>
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
@@ -3930,10 +4174,10 @@
         <v>0</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>0.1576876655884257</v>
+        <v>0.1560336873549507</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.1676876655884257</v>
+        <v>0.1660336873549507</v>
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
@@ -3959,10 +4203,10 @@
         <v>0.01</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>0.1576876655884257</v>
+        <v>0.1560336873549507</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.1676876655884257</v>
+        <v>0.1660336873549507</v>
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
@@ -4070,11 +4314,11 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>International Developed Equity</t>
+          <t>U.S. Value</t>
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C27" s="7" t="n">
         <v>0.2</v>
@@ -4091,14 +4335,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Emerging Markets Equity</t>
+          <t>U.S. Growth</t>
         </is>
       </c>
       <c r="B28" s="7" t="n">
         <v>0</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
@@ -4112,14 +4356,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>U.S. REITs</t>
+          <t>U.S. Income</t>
         </is>
       </c>
       <c r="B29" s="7" t="n">
         <v>0</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
@@ -4133,14 +4377,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>U.S. Quality</t>
         </is>
       </c>
       <c r="B30" s="7" t="n">
         <v>0</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
@@ -4154,14 +4398,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Income U.S. - U.S. Treasury</t>
+          <t>International Developed Equity</t>
         </is>
       </c>
       <c r="B31" s="7" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>0.45</v>
+        <v>0.2</v>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
@@ -4175,14 +4419,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Income U.S. Government Related</t>
+          <t>Emerging Markets Equity</t>
         </is>
       </c>
       <c r="B32" s="7" t="n">
         <v>0</v>
       </c>
       <c r="C32" s="7" t="n">
-        <v>0.35</v>
+        <v>0.1</v>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
@@ -4196,14 +4440,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Income U.S. Corporate</t>
+          <t>U.S. REITs</t>
         </is>
       </c>
       <c r="B33" s="7" t="n">
         <v>0</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
@@ -4217,14 +4461,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Income U.S. Securitized</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="B34" s="7" t="n">
         <v>0</v>
       </c>
       <c r="C34" s="7" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
@@ -4238,14 +4482,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Fixed Income International</t>
+          <t>Income U.S. - U.S. Treasury</t>
         </is>
       </c>
       <c r="B35" s="7" t="n">
         <v>0</v>
       </c>
       <c r="C35" s="7" t="n">
-        <v>0.1</v>
+        <v>0.45</v>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
@@ -4259,14 +4503,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Other Fixed Income</t>
+          <t>Income U.S. Government Related</t>
         </is>
       </c>
       <c r="B36" s="7" t="n">
         <v>0</v>
       </c>
       <c r="C36" s="7" t="n">
-        <v>0.01</v>
+        <v>0.35</v>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
@@ -4280,14 +4524,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Income U.S. Corporate</t>
         </is>
       </c>
       <c r="B37" s="7" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="C37" s="7" t="n">
-        <v>0.01</v>
+        <v>0.4</v>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
@@ -4297,6 +4541,90 @@
       <c r="E37" s="7" t="n"/>
       <c r="F37" s="7" t="n"/>
       <c r="G37" s="9" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Income U.S. Securitized</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="7" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>Direct asset-level bounds used by optimizer</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="n"/>
+      <c r="F38" s="7" t="n"/>
+      <c r="G38" s="9" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Fixed Income International</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>Direct asset-level bounds used by optimizer</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="n"/>
+      <c r="F39" s="7" t="n"/>
+      <c r="G39" s="9" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Other Fixed Income</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="7" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>Direct asset-level bounds used by optimizer</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="n"/>
+      <c r="F40" s="7" t="n"/>
+      <c r="G40" s="9" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C41" s="7" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>Direct asset-level bounds used by optimizer</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="n"/>
+      <c r="F41" s="7" t="n"/>
+      <c r="G41" s="9" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4510,7 +4838,7 @@
         </is>
       </c>
       <c r="B7" s="10">
-        <f>'MVO Detail'!C15</f>
+        <f>'MVO Detail'!C19</f>
         <v/>
       </c>
       <c r="C7" s="10" t="n">
@@ -4536,7 +4864,7 @@
         </is>
       </c>
       <c r="B8" s="10">
-        <f>'MVO Detail'!D15</f>
+        <f>'MVO Detail'!D19</f>
         <v/>
       </c>
       <c r="C8" s="10" t="n">
@@ -4562,7 +4890,7 @@
         </is>
       </c>
       <c r="B9" s="10">
-        <f>'MVO Detail'!E15</f>
+        <f>'MVO Detail'!E19</f>
         <v/>
       </c>
       <c r="C9" s="10" t="n">
@@ -4588,7 +4916,7 @@
         </is>
       </c>
       <c r="B10" s="10">
-        <f>'MVO Detail'!F15</f>
+        <f>'MVO Detail'!F19</f>
         <v/>
       </c>
       <c r="C10" s="10" t="n">
@@ -4614,7 +4942,7 @@
         </is>
       </c>
       <c r="B11" s="10">
-        <f>'MVO Detail'!G15</f>
+        <f>'MVO Detail'!G19</f>
         <v/>
       </c>
       <c r="C11" s="10" t="n">

--- a/outputs/paul_asset_allocation_model.xlsx
+++ b/outputs/paul_asset_allocation_model.xlsx
@@ -939,19 +939,19 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>0.05748</v>
+        <v>0.057583</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>0.083052</v>
+        <v>0.083258</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>0.318835</v>
+        <v>0.319288</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.300114</v>
+        <v>0.308236</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.689886</v>
+        <v>0.681764</v>
       </c>
       <c r="G11" s="5" t="n">
         <v>0</v>
@@ -960,10 +960,10 @@
         <v>0.01</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0.07305185153905434</v>
+        <v>0.07325822490381834</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>0.08305185153905435</v>
+        <v>0.08325822490381835</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
@@ -978,19 +978,19 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>0.065857</v>
+        <v>0.064982</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>0.113714</v>
+        <v>0.113803</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>0.306534</v>
+        <v>0.2986</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0.570027</v>
+        <v>0.55</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.419973</v>
+        <v>0.44</v>
       </c>
       <c r="G12" s="5" t="n">
         <v>0</v>
@@ -999,10 +999,10 @@
         <v>0.01</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.1037143091201067</v>
+        <v>0.1038034110912644</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0.1137143091201067</v>
+        <v>0.1138034110912644</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
@@ -1017,19 +1017,19 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>0.068508</v>
+        <v>0.066707</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0.126688</v>
+        <v>0.126879</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>0.296068</v>
+        <v>0.281421</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0.69333</v>
+        <v>0.65838</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.29667</v>
+        <v>0.33162</v>
       </c>
       <c r="G13" s="5" t="n">
         <v>0</v>
@@ -1038,10 +1038,10 @@
         <v>0.01</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>0.1206880986447292</v>
+        <v>0.1208794244448776</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>0.1266880986447292</v>
+        <v>0.1268794244448776</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
@@ -1056,19 +1056,19 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>0.071757</v>
+        <v>0.068758</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>0.14506</v>
+        <v>0.14487</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>0.280964</v>
+        <v>0.260632</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0.828889</v>
+        <v>0.828489</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.161111</v>
+        <v>0.161511</v>
       </c>
       <c r="G14" s="5" t="n">
         <v>0</v>
@@ -1077,10 +1077,10 @@
         <v>0.01</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>0.1350603109512361</v>
+        <v>0.1348696799445297</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>0.1450603109512361</v>
+        <v>0.1448696799445297</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
@@ -1095,19 +1095,19 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>0.07421</v>
+        <v>0.070271</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>0.164487</v>
+        <v>0.158955</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>0.262695</v>
+        <v>0.24706</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.99</v>
+        <v>0.960127</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0</v>
+        <v>0.029873</v>
       </c>
       <c r="G15" s="5" t="n">
         <v>0</v>
@@ -1116,10 +1116,10 @@
         <v>0.01</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>0.1560336873549507</v>
+        <v>0.1489551336606144</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>0.1660336873549507</v>
+        <v>0.1589551336606145</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
@@ -1234,19 +1234,19 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>0.05748</v>
+        <v>0.057583</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>0.083052</v>
+        <v>0.083258</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>0.318835</v>
+        <v>0.319288</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0.300114</v>
+        <v>0.308236</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0.689886</v>
+        <v>0.681764</v>
       </c>
       <c r="G20" s="5" t="n">
         <v>0</v>
@@ -1255,10 +1255,10 @@
         <v>0.01</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>0.07305185153905434</v>
+        <v>0.07325822490381834</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>0.08305185153905435</v>
+        <v>0.08325822490381835</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
@@ -1273,19 +1273,19 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>0.065857</v>
+        <v>0.064982</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>0.113714</v>
+        <v>0.113803</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>0.306534</v>
+        <v>0.2986</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0.570027</v>
+        <v>0.55</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.419973</v>
+        <v>0.44</v>
       </c>
       <c r="G21" s="5" t="n">
         <v>0</v>
@@ -1294,10 +1294,10 @@
         <v>0.01</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>0.1037143091201067</v>
+        <v>0.1038034110912644</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>0.1137143091201067</v>
+        <v>0.1138034110912644</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
@@ -1312,19 +1312,19 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>0.068508</v>
+        <v>0.066707</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>0.126688</v>
+        <v>0.126879</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>0.296068</v>
+        <v>0.281421</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0.69333</v>
+        <v>0.65838</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.29667</v>
+        <v>0.33162</v>
       </c>
       <c r="G22" s="5" t="n">
         <v>0</v>
@@ -1333,10 +1333,10 @@
         <v>0.01</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>0.1206880986447292</v>
+        <v>0.1208794244448776</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>0.1266880986447292</v>
+        <v>0.1268794244448776</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
@@ -1351,19 +1351,19 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>0.071757</v>
+        <v>0.068758</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>0.14506</v>
+        <v>0.14487</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>0.280964</v>
+        <v>0.260632</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0.828889</v>
+        <v>0.828489</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0.161111</v>
+        <v>0.161511</v>
       </c>
       <c r="G23" s="5" t="n">
         <v>0</v>
@@ -1372,10 +1372,10 @@
         <v>0.01</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>0.1350603109512361</v>
+        <v>0.1348696799445297</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>0.1450603109512361</v>
+        <v>0.1448696799445297</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
@@ -1390,19 +1390,19 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>0.07421</v>
+        <v>0.070271</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>0.164487</v>
+        <v>0.158955</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>0.262695</v>
+        <v>0.24706</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>0.99</v>
+        <v>0.960127</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0</v>
+        <v>0.029873</v>
       </c>
       <c r="G24" s="5" t="n">
         <v>0</v>
@@ -1411,10 +1411,10 @@
         <v>0.01</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>0.1560336873549507</v>
+        <v>0.1489551336606144</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>0.1660336873549507</v>
+        <v>0.1589551336606145</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>0.2</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>0.2</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>0.2</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>0.2</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -1754,10 +1754,10 @@
         <v>0.1762945661402543</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -2186,10 +2186,10 @@
         <v>0.2</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>0.2</v>
+        <v>0.308973</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.2</v>
+        <v>0.428985</v>
       </c>
     </row>
     <row r="3">
@@ -2210,13 +2210,13 @@
         <v>0</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0</v>
+        <v>0.06838</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="4">
@@ -2261,16 +2261,16 @@
         <v>0</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.09333</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.2</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.2</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -2294,10 +2294,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0</v>
+        <v>0.029516</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0</v>
+        <v>0.041141</v>
       </c>
     </row>
     <row r="7">
@@ -2312,19 +2312,19 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0.000114</v>
+        <v>0.055082</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>0.170027</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.2</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.2</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.2</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -2342,16 +2342,16 @@
         <v>0</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -2366,19 +2366,19 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0.1</v>
+        <v>0.053154</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="10">
@@ -2396,16 +2396,16 @@
         <v>0</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.028889</v>
+        <v>0.03</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="11">
@@ -2474,7 +2474,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0.002832</v>
+        <v>0.007406</v>
       </c>
       <c r="D13" s="5" t="n">
         <v>0</v>
@@ -2501,7 +2501,7 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>0.147054</v>
+        <v>0.134358</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>0</v>
@@ -2531,16 +2531,16 @@
         <v>0.4</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>0.279973</v>
+        <v>0.372347</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.15667</v>
+        <v>0.32162</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.151111</v>
+        <v>0.151511</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0</v>
+        <v>0.019873</v>
       </c>
     </row>
     <row r="16">
@@ -2561,7 +2561,7 @@
         <v>0.03</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="F16" s="5" t="n">
         <v>0</v>
@@ -2585,10 +2585,10 @@
         <v>0.1</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>0.1</v>
+        <v>0.027653</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F17" s="5" t="n">
         <v>0</v>
@@ -2621,7 +2621,7 @@
         <v>0.01</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="19">
@@ -2791,13 +2791,13 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>0.010611</v>
+        <v>0.010776</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>0.074644</v>
+        <v>0.073641</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>-0.273156</v>
+        <v>-0.274631</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>0.3</v>
@@ -2812,10 +2812,10 @@
         <v>0.01</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>0.07305185153905434</v>
+        <v>0.07325822490381834</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>0.08305185153905435</v>
+        <v>0.08325822490381835</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
@@ -2830,13 +2830,13 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>0.004365</v>
+        <v>0.003704</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>0.103714</v>
+        <v>0.103803</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>-0.256814</v>
+        <v>-0.262963</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>0.55</v>
@@ -2851,10 +2851,10 @@
         <v>0.01</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>0.1037143091201067</v>
+        <v>0.1038034110912644</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>0.1137143091201067</v>
+        <v>0.1138034110912644</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
@@ -2869,13 +2869,13 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>0.001432</v>
+        <v>7.8e-05</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>0.120688</v>
+        <v>0.120879</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>-0.244997</v>
+        <v>-0.255813</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>0.65</v>
@@ -2890,10 +2890,10 @@
         <v>0.01</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>0.1206880986447292</v>
+        <v>0.1208794244448776</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>0.1266880986447292</v>
+        <v>0.1268794244448776</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
@@ -2908,19 +2908,19 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>-0.002169</v>
+        <v>-0.004068</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>0.13506</v>
+        <v>0.13487</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>-0.245587</v>
+        <v>-0.260017</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.75</v>
+        <v>0.751502</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.24</v>
+        <v>0.238498</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>0</v>
@@ -2929,10 +2929,10 @@
         <v>0.01</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>0.1350603109512361</v>
+        <v>0.1348696799445297</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>0.1450603109512361</v>
+        <v>0.1448696799445297</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
@@ -2947,19 +2947,19 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>-0.008129000000000001</v>
+        <v>-0.008784</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0.156034</v>
+        <v>0.148955</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>-0.25077</v>
+        <v>-0.267084</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.95519</v>
+        <v>0.9</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.03481</v>
+        <v>0.09</v>
       </c>
       <c r="G7" s="5" t="n">
         <v>0</v>
@@ -2968,10 +2968,10 @@
         <v>0.01</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>0.1560336873549507</v>
+        <v>0.1489551336606144</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>0.1660336873549507</v>
+        <v>0.1589551336606145</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
@@ -3086,19 +3086,19 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>0.05748</v>
+        <v>0.057583</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>0.083052</v>
+        <v>0.083258</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>0.318835</v>
+        <v>0.319288</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0.300114</v>
+        <v>0.308236</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.689886</v>
+        <v>0.681764</v>
       </c>
       <c r="G12" s="5" t="n">
         <v>0</v>
@@ -3107,10 +3107,10 @@
         <v>0.01</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.07305185153905434</v>
+        <v>0.07325822490381834</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0.08305185153905435</v>
+        <v>0.08325822490381835</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
@@ -3125,19 +3125,19 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>0.065857</v>
+        <v>0.064982</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0.113714</v>
+        <v>0.113803</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>0.306534</v>
+        <v>0.2986</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0.570027</v>
+        <v>0.55</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.419973</v>
+        <v>0.44</v>
       </c>
       <c r="G13" s="5" t="n">
         <v>0</v>
@@ -3146,10 +3146,10 @@
         <v>0.01</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>0.1037143091201067</v>
+        <v>0.1038034110912644</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>0.1137143091201067</v>
+        <v>0.1138034110912644</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
@@ -3164,19 +3164,19 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>0.068508</v>
+        <v>0.066707</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>0.126688</v>
+        <v>0.126879</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>0.296068</v>
+        <v>0.281421</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0.69333</v>
+        <v>0.65838</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.29667</v>
+        <v>0.33162</v>
       </c>
       <c r="G14" s="5" t="n">
         <v>0</v>
@@ -3185,10 +3185,10 @@
         <v>0.01</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>0.1206880986447292</v>
+        <v>0.1208794244448776</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>0.1266880986447292</v>
+        <v>0.1268794244448776</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
@@ -3203,19 +3203,19 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>0.071757</v>
+        <v>0.068758</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>0.14506</v>
+        <v>0.14487</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>0.280964</v>
+        <v>0.260632</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.828889</v>
+        <v>0.828489</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.161111</v>
+        <v>0.161511</v>
       </c>
       <c r="G15" s="5" t="n">
         <v>0</v>
@@ -3224,10 +3224,10 @@
         <v>0.01</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>0.1350603109512361</v>
+        <v>0.1348696799445297</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>0.1450603109512361</v>
+        <v>0.1448696799445297</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
@@ -3242,19 +3242,19 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>0.07421</v>
+        <v>0.070271</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>0.164487</v>
+        <v>0.158955</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>0.262695</v>
+        <v>0.24706</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0.99</v>
+        <v>0.960127</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0</v>
+        <v>0.029873</v>
       </c>
       <c r="G16" s="5" t="n">
         <v>0</v>
@@ -3263,10 +3263,10 @@
         <v>0.01</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>0.1560336873549507</v>
+        <v>0.1489551336606144</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>0.1660336873549507</v>
+        <v>0.1589551336606145</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
@@ -3381,19 +3381,19 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>0.110162</v>
+        <v>0.110298</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>0.083052</v>
+        <v>0.083258</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>0.953166</v>
+        <v>0.9524359999999999</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0.422974</v>
+        <v>0.42227</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.567026</v>
+        <v>0.56773</v>
       </c>
       <c r="G21" s="5" t="n">
         <v>0</v>
@@ -3402,10 +3402,10 @@
         <v>0.01</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>0.07305185153905434</v>
+        <v>0.07325822490381834</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>0.08305185153905435</v>
+        <v>0.08325822490381835</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
@@ -3420,13 +3420,13 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>0.131705</v>
+        <v>0.130395</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>0.113714</v>
+        <v>0.113803</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>0.885598</v>
+        <v>0.873393</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>0.64</v>
@@ -3441,10 +3441,10 @@
         <v>0.01</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>0.1037143091201067</v>
+        <v>0.1038034110912644</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>0.1137143091201067</v>
+        <v>0.1138034110912644</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
@@ -3459,19 +3459,19 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>0.140011</v>
+        <v>0.137434</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>0.126688</v>
+        <v>0.126879</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>0.860466</v>
+        <v>0.838866</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0.74</v>
+        <v>0.739994</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0.25</v>
+        <v>0.250005</v>
       </c>
       <c r="G23" s="5" t="n">
         <v>0</v>
@@ -3480,10 +3480,10 @@
         <v>0.01</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>0.1206880986447292</v>
+        <v>0.1208794244448776</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>0.1266880986447292</v>
+        <v>0.1268794244448776</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
@@ -3498,13 +3498,13 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>0.150475</v>
+        <v>0.146322</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>0.14506</v>
+        <v>0.14487</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>0.823622</v>
+        <v>0.7960429999999999</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>0.85</v>
@@ -3519,10 +3519,10 @@
         <v>0.01</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>0.1350603109512361</v>
+        <v>0.1348696799445297</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>0.1450603109512361</v>
+        <v>0.1448696799445297</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
@@ -3537,19 +3537,19 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>0.16197</v>
+        <v>0.153406</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>0.166034</v>
+        <v>0.158955</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>0.788813</v>
+        <v>0.770066</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>0.99</v>
+        <v>0.963315</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>0</v>
+        <v>0.026685</v>
       </c>
       <c r="G25" s="5" t="n">
         <v>0</v>
@@ -3558,10 +3558,10 @@
         <v>0.01</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>0.1560336873549507</v>
+        <v>0.1489551336606144</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>0.1660336873549507</v>
+        <v>0.1589551336606145</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
@@ -3652,10 +3652,10 @@
         <v>0.5</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>0.07305185153905434</v>
+        <v>0.07325822490381834</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>0.08305185153905435</v>
+        <v>0.08325822490381835</v>
       </c>
       <c r="G2" s="9" t="inlineStr">
         <is>
@@ -3681,10 +3681,10 @@
         <v>0.75</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>0.07305185153905434</v>
+        <v>0.07325822490381834</v>
       </c>
       <c r="F3" s="7" t="n">
-        <v>0.08305185153905435</v>
+        <v>0.08325822490381835</v>
       </c>
       <c r="G3" s="9" t="inlineStr">
         <is>
@@ -3710,10 +3710,10 @@
         <v>0</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>0.07305185153905434</v>
+        <v>0.07325822490381834</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>0.08305185153905435</v>
+        <v>0.08325822490381835</v>
       </c>
       <c r="G4" s="9" t="inlineStr">
         <is>
@@ -3739,10 +3739,10 @@
         <v>0.01</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>0.07305185153905434</v>
+        <v>0.07325822490381834</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>0.08305185153905435</v>
+        <v>0.08325822490381835</v>
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
@@ -3768,10 +3768,10 @@
         <v>0.65</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>0.1037143091201067</v>
+        <v>0.1038034110912644</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>0.1137143091201067</v>
+        <v>0.1138034110912644</v>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
@@ -3797,10 +3797,10 @@
         <v>0.55</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>0.1037143091201067</v>
+        <v>0.1038034110912644</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>0.1137143091201067</v>
+        <v>0.1138034110912644</v>
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
@@ -3826,10 +3826,10 @@
         <v>0</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>0.1037143091201067</v>
+        <v>0.1038034110912644</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>0.1137143091201067</v>
+        <v>0.1138034110912644</v>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
@@ -3855,10 +3855,10 @@
         <v>0.01</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>0.1037143091201067</v>
+        <v>0.1038034110912644</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>0.1137143091201067</v>
+        <v>0.1138034110912644</v>
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
@@ -3884,10 +3884,10 @@
         <v>0.75</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>0.1206880986447292</v>
+        <v>0.1208794244448776</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>0.1266880986447292</v>
+        <v>0.1268794244448776</v>
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
@@ -3913,10 +3913,10 @@
         <v>0.4</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>0.1206880986447292</v>
+        <v>0.1208794244448776</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>0.1266880986447292</v>
+        <v>0.1268794244448776</v>
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
@@ -3942,10 +3942,10 @@
         <v>0</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>0.1206880986447292</v>
+        <v>0.1208794244448776</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>0.1266880986447292</v>
+        <v>0.1268794244448776</v>
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
@@ -3971,10 +3971,10 @@
         <v>0.01</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>0.1206880986447292</v>
+        <v>0.1208794244448776</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>0.1266880986447292</v>
+        <v>0.1268794244448776</v>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
@@ -4000,10 +4000,10 @@
         <v>0.85</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>0.1350603109512361</v>
+        <v>0.1348696799445297</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>0.1450603109512361</v>
+        <v>0.1448696799445297</v>
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
@@ -4029,10 +4029,10 @@
         <v>0.25</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>0.1350603109512361</v>
+        <v>0.1348696799445297</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>0.1450603109512361</v>
+        <v>0.1448696799445297</v>
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
@@ -4058,10 +4058,10 @@
         <v>0</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>0.1350603109512361</v>
+        <v>0.1348696799445297</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>0.1450603109512361</v>
+        <v>0.1448696799445297</v>
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
@@ -4087,10 +4087,10 @@
         <v>0.01</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>0.1350603109512361</v>
+        <v>0.1348696799445297</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>0.1450603109512361</v>
+        <v>0.1448696799445297</v>
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
@@ -4116,10 +4116,10 @@
         <v>1</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>0.1560336873549507</v>
+        <v>0.1489551336606144</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>0.1660336873549507</v>
+        <v>0.1589551336606145</v>
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
@@ -4145,10 +4145,10 @@
         <v>0.12</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>0.1560336873549507</v>
+        <v>0.1489551336606144</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>0.1660336873549507</v>
+        <v>0.1589551336606145</v>
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
@@ -4174,10 +4174,10 @@
         <v>0</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>0.1560336873549507</v>
+        <v>0.1489551336606144</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.1660336873549507</v>
+        <v>0.1589551336606145</v>
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
@@ -4203,10 +4203,10 @@
         <v>0.01</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>0.1560336873549507</v>
+        <v>0.1489551336606144</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.1660336873549507</v>
+        <v>0.1589551336606145</v>
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>0</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>0</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>0</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>0.2</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>0</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>0.2</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         <v>0</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>0.2</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>0</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>0.2</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
@@ -4402,10 +4402,10 @@
         </is>
       </c>
       <c r="B31" s="7" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>0</v>
       </c>
       <c r="C32" s="7" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
